--- a/Rescatables20232.xlsx
+++ b/Rescatables20232.xlsx
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1782" uniqueCount="545">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1714" uniqueCount="548">
   <si>
     <t>Num_Cont</t>
   </si>
@@ -477,6 +477,9 @@
     <t>GUTIERREZ</t>
   </si>
   <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
     <t>PALOMARES</t>
   </si>
   <si>
@@ -510,6 +513,9 @@
     <t>POOT</t>
   </si>
   <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
     <t>RIVERA</t>
   </si>
   <si>
@@ -564,6 +570,9 @@
     <t>KAROL BALAAM</t>
   </si>
   <si>
+    <t>DENISSE</t>
+  </si>
+  <si>
     <t>YASMIN</t>
   </si>
   <si>
@@ -588,6 +597,9 @@
     <t>SAMANTHA BETHANY</t>
   </si>
   <si>
+    <t>Pensamiento matemático II</t>
+  </si>
+  <si>
     <t>COYOHUA</t>
   </si>
   <si>
@@ -627,9 +639,6 @@
     <t>DURAND</t>
   </si>
   <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
     <t>PANZO</t>
   </si>
   <si>
@@ -693,6 +702,9 @@
     <t>Lengua y comunicación II</t>
   </si>
   <si>
+    <t>ALVAREZ</t>
+  </si>
+  <si>
     <t>ARRIETA</t>
   </si>
   <si>
@@ -735,6 +747,9 @@
     <t>BORBONIO</t>
   </si>
   <si>
+    <t>VOTE</t>
+  </si>
+  <si>
     <t>NAVA</t>
   </si>
   <si>
@@ -747,9 +762,6 @@
     <t>HILARIO</t>
   </si>
   <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
     <t>ANDRADE</t>
   </si>
   <si>
@@ -786,6 +798,9 @@
     <t>VASQUEZ</t>
   </si>
   <si>
+    <t>CAMILO</t>
+  </si>
+  <si>
     <t>IRMA GUADALUPE</t>
   </si>
   <si>
@@ -876,400 +891,394 @@
     <t>BRENDA</t>
   </si>
   <si>
+    <t>TOMA MUESTRAS BIOLÓGICAS</t>
+  </si>
+  <si>
+    <t>DE LA LUZ</t>
+  </si>
+  <si>
+    <t>MERINO</t>
+  </si>
+  <si>
+    <t>QUERO</t>
+  </si>
+  <si>
+    <t>JERONIMO</t>
+  </si>
+  <si>
+    <t>AVELINO</t>
+  </si>
+  <si>
+    <t>MACARIO</t>
+  </si>
+  <si>
+    <t>RUBEN DE JESUS</t>
+  </si>
+  <si>
+    <t>DANIEL</t>
+  </si>
+  <si>
+    <t>DIEGO</t>
+  </si>
+  <si>
+    <t>ALEXANDER</t>
+  </si>
+  <si>
+    <t>DIEGO JESUS</t>
+  </si>
+  <si>
+    <t>LUIS</t>
+  </si>
+  <si>
+    <t>KEVIN</t>
+  </si>
+  <si>
+    <t>CESAR</t>
+  </si>
+  <si>
+    <t>ANGEL GUILLERMO</t>
+  </si>
+  <si>
+    <t>SHERLIN</t>
+  </si>
+  <si>
+    <t>CÁLCULO DIFERENCIAL</t>
+  </si>
+  <si>
+    <t>INGLÉS IV</t>
+  </si>
+  <si>
+    <t>ECOLOGÍA</t>
+  </si>
+  <si>
+    <t>OLMOS</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>PRADO</t>
+  </si>
+  <si>
+    <t>SOTO</t>
+  </si>
+  <si>
+    <t>ANETTE</t>
+  </si>
+  <si>
+    <t>AHILY</t>
+  </si>
+  <si>
+    <t>CAMARILLO</t>
+  </si>
+  <si>
+    <t>CORRO</t>
+  </si>
+  <si>
+    <t>SUAREZ</t>
+  </si>
+  <si>
+    <t>OLMEDO</t>
+  </si>
+  <si>
+    <t>ALFONSO</t>
+  </si>
+  <si>
+    <t>EVANGELISTA</t>
+  </si>
+  <si>
+    <t>DINORAH AZUL</t>
+  </si>
+  <si>
+    <t>JULIO</t>
+  </si>
+  <si>
+    <t>SAUL KOURCHENKOV</t>
+  </si>
+  <si>
+    <t>SERGIO FARITH</t>
+  </si>
+  <si>
+    <t>GUSTAVO</t>
+  </si>
+  <si>
+    <t>DESARROLLA APLICACIONES QUE SE EJECUTAN EN EL SERVIDOR</t>
+  </si>
+  <si>
+    <t>DESARROLLA APLICACIONES QUE SE EJECUTAN EN EL CLIENTE</t>
+  </si>
+  <si>
+    <t>CONSTRUYE PÁGINAS WEB</t>
+  </si>
+  <si>
+    <t>OREA</t>
+  </si>
+  <si>
+    <t>PALMA</t>
+  </si>
+  <si>
+    <t>MACHORRO</t>
+  </si>
+  <si>
+    <t>ORTEGA</t>
+  </si>
+  <si>
+    <t>RANGEL</t>
+  </si>
+  <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
+    <t>PALACIOS</t>
+  </si>
+  <si>
+    <t>MORA</t>
+  </si>
+  <si>
+    <t>ESPARZA</t>
+  </si>
+  <si>
+    <t>JOSE MANUEL</t>
+  </si>
+  <si>
+    <t>DIEGO ANTONIO</t>
+  </si>
+  <si>
+    <t>ROBERTO</t>
+  </si>
+  <si>
+    <t>FATIMA</t>
+  </si>
+  <si>
+    <t>DANIELA</t>
+  </si>
+  <si>
+    <t>DANIEL ELEAZAR</t>
+  </si>
+  <si>
+    <t>JIMENA</t>
+  </si>
+  <si>
+    <t>CLAUDIA PAOLA</t>
+  </si>
+  <si>
+    <t>ANGELES VALERIA</t>
+  </si>
+  <si>
+    <t>JESUS ALEJANDRO</t>
+  </si>
+  <si>
+    <t>KEVIN RAUL</t>
+  </si>
+  <si>
+    <t>FÍSICA I</t>
+  </si>
+  <si>
+    <t>EVALÚA EL DESEMPEÑO DE LA ORGANIZACIÓN UTILIZANDO HERRAMIENTAS DE CALIDAD</t>
+  </si>
+  <si>
+    <t>PALOMINO</t>
+  </si>
+  <si>
+    <t>MELCHOR</t>
+  </si>
+  <si>
+    <t>CONTRERAS</t>
+  </si>
+  <si>
+    <t>MENDOZA</t>
+  </si>
+  <si>
+    <t>CARLOS YAEL</t>
+  </si>
+  <si>
+    <t>JOSE RAUL</t>
+  </si>
+  <si>
+    <t>AARON MIGUEL</t>
+  </si>
+  <si>
+    <t>GEOVANNI</t>
+  </si>
+  <si>
+    <t>ALDAHIR</t>
+  </si>
+  <si>
+    <t>JORGE IVAN</t>
+  </si>
+  <si>
+    <t>DAMIAN</t>
+  </si>
+  <si>
+    <t>SALAS</t>
+  </si>
+  <si>
+    <t>MELISA VIANNEY</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>MOLOHUA</t>
+  </si>
+  <si>
+    <t>MIXCOHUA</t>
+  </si>
+  <si>
+    <t>AYLIN MELISSA</t>
+  </si>
+  <si>
+    <t>CRISTHIAN</t>
+  </si>
+  <si>
+    <t>CRISTIAN FERNANDO</t>
+  </si>
+  <si>
+    <t>YAHIR</t>
+  </si>
+  <si>
+    <t>CANDIDO</t>
+  </si>
+  <si>
+    <t>TEMAS DE FÍSICA</t>
+  </si>
+  <si>
+    <t>TEMAS DE FILOSOFÍA</t>
+  </si>
+  <si>
+    <t>PROBABILIDAD Y ESTADÍSTICA</t>
+  </si>
+  <si>
+    <t>BAEZ</t>
+  </si>
+  <si>
+    <t>GAEL JARED</t>
+  </si>
+  <si>
+    <t>JOSUE EDUARDO</t>
+  </si>
+  <si>
+    <t>NAHOMI ITZAYANA</t>
+  </si>
+  <si>
+    <t>MATEMÁTICAS APLICADAS</t>
+  </si>
+  <si>
+    <t>LIZBETH JOSELYN</t>
+  </si>
+  <si>
+    <t>INTRODUCCIÓN A LA ECONOMÍA</t>
+  </si>
+  <si>
+    <t>LORENZO</t>
+  </si>
+  <si>
+    <t>ARELLANO</t>
+  </si>
+  <si>
+    <t>NAVARRO</t>
+  </si>
+  <si>
+    <t>PIEDRAS</t>
+  </si>
+  <si>
+    <t>CUICAHUA</t>
+  </si>
+  <si>
+    <t>JORGE GUILLERMO</t>
+  </si>
+  <si>
+    <t>WENCESLAO</t>
+  </si>
+  <si>
+    <t>JORGE MARIO</t>
+  </si>
+  <si>
+    <t>LUIS REY</t>
+  </si>
+  <si>
+    <t>DARINKA</t>
+  </si>
+  <si>
+    <t>GREGORIO</t>
+  </si>
+  <si>
+    <t>ZUÑIGA</t>
+  </si>
+  <si>
+    <t>ZARATE</t>
+  </si>
+  <si>
+    <t>MONGE</t>
+  </si>
+  <si>
+    <t>ESPINDOLA</t>
+  </si>
+  <si>
+    <t>NAHOMY</t>
+  </si>
+  <si>
+    <t>JOSE RAFAEL</t>
+  </si>
+  <si>
+    <t>DIANA CRISTINA</t>
+  </si>
+  <si>
+    <t>DIEGO EMILIO</t>
+  </si>
+  <si>
+    <t>ROSA ITZEL</t>
+  </si>
+  <si>
+    <t>TEMAS DE BIOLOGÍA CONTEMPORÁNEA</t>
+  </si>
+  <si>
+    <t>BUSTOS</t>
+  </si>
+  <si>
+    <t>CERONIO</t>
+  </si>
+  <si>
+    <t>LARA</t>
+  </si>
+  <si>
+    <t>TEQUIHUATLE</t>
+  </si>
+  <si>
+    <t>COCOTLE</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>ANGEL CHARBEL</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>JOSE EMILIANO</t>
+  </si>
+  <si>
+    <t>JOSE ALDAIR</t>
+  </si>
+  <si>
+    <t>EMMANUEL</t>
+  </si>
+  <si>
+    <t>KEVYN DANIEL</t>
+  </si>
+  <si>
+    <t>ROBBIE ALONSO</t>
+  </si>
+  <si>
+    <t>ANTHONY</t>
+  </si>
+  <si>
+    <t>ISAAC</t>
+  </si>
+  <si>
     <t>Ingles II</t>
-  </si>
-  <si>
-    <t>Pensamiento matemático II</t>
-  </si>
-  <si>
-    <t>TOMA MUESTRAS BIOLÓGICAS</t>
-  </si>
-  <si>
-    <t>ALVAREZ</t>
-  </si>
-  <si>
-    <t>DE LA LUZ</t>
-  </si>
-  <si>
-    <t>MERINO</t>
-  </si>
-  <si>
-    <t>QUERO</t>
-  </si>
-  <si>
-    <t>JERONIMO</t>
-  </si>
-  <si>
-    <t>AVELINO</t>
-  </si>
-  <si>
-    <t>MACARIO</t>
-  </si>
-  <si>
-    <t>RUBEN DE JESUS</t>
-  </si>
-  <si>
-    <t>DANIEL</t>
-  </si>
-  <si>
-    <t>DIEGO</t>
-  </si>
-  <si>
-    <t>ALEXANDER</t>
-  </si>
-  <si>
-    <t>DIEGO JESUS</t>
-  </si>
-  <si>
-    <t>LUIS</t>
-  </si>
-  <si>
-    <t>KEVIN</t>
-  </si>
-  <si>
-    <t>CESAR</t>
-  </si>
-  <si>
-    <t>ANGEL GUILLERMO</t>
-  </si>
-  <si>
-    <t>SHERLIN</t>
-  </si>
-  <si>
-    <t>CÁLCULO DIFERENCIAL</t>
-  </si>
-  <si>
-    <t>INGLÉS IV</t>
-  </si>
-  <si>
-    <t>ECOLOGÍA</t>
-  </si>
-  <si>
-    <t>OLMOS</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>PRADO</t>
-  </si>
-  <si>
-    <t>SOTO</t>
-  </si>
-  <si>
-    <t>ANETTE</t>
-  </si>
-  <si>
-    <t>AHILY</t>
-  </si>
-  <si>
-    <t>CAMARILLO</t>
-  </si>
-  <si>
-    <t>CORRO</t>
-  </si>
-  <si>
-    <t>SUAREZ</t>
-  </si>
-  <si>
-    <t>OLMEDO</t>
-  </si>
-  <si>
-    <t>ALFONSO</t>
-  </si>
-  <si>
-    <t>EVANGELISTA</t>
-  </si>
-  <si>
-    <t>DINORAH AZUL</t>
-  </si>
-  <si>
-    <t>JULIO</t>
-  </si>
-  <si>
-    <t>SAUL KOURCHENKOV</t>
-  </si>
-  <si>
-    <t>SERGIO FARITH</t>
-  </si>
-  <si>
-    <t>GUSTAVO</t>
-  </si>
-  <si>
-    <t>DESARROLLA APLICACIONES QUE SE EJECUTAN EN EL SERVIDOR</t>
-  </si>
-  <si>
-    <t>DESARROLLA APLICACIONES QUE SE EJECUTAN EN EL CLIENTE</t>
-  </si>
-  <si>
-    <t>CONSTRUYE PÁGINAS WEB</t>
-  </si>
-  <si>
-    <t>OREA</t>
-  </si>
-  <si>
-    <t>PALMA</t>
-  </si>
-  <si>
-    <t>MACHORRO</t>
-  </si>
-  <si>
-    <t>ORTEGA</t>
-  </si>
-  <si>
-    <t>RANGEL</t>
-  </si>
-  <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>PALACIOS</t>
-  </si>
-  <si>
-    <t>MORA</t>
-  </si>
-  <si>
-    <t>ESPARZA</t>
-  </si>
-  <si>
-    <t>JOSE MANUEL</t>
-  </si>
-  <si>
-    <t>DIEGO ANTONIO</t>
-  </si>
-  <si>
-    <t>ROBERTO</t>
-  </si>
-  <si>
-    <t>FATIMA</t>
-  </si>
-  <si>
-    <t>DANIELA</t>
-  </si>
-  <si>
-    <t>DANIEL ELEAZAR</t>
-  </si>
-  <si>
-    <t>JIMENA</t>
-  </si>
-  <si>
-    <t>CLAUDIA PAOLA</t>
-  </si>
-  <si>
-    <t>ANGELES VALERIA</t>
-  </si>
-  <si>
-    <t>JESUS ALEJANDRO</t>
-  </si>
-  <si>
-    <t>KEVIN RAUL</t>
-  </si>
-  <si>
-    <t>FÍSICA I</t>
-  </si>
-  <si>
-    <t>EVALÚA EL DESEMPEÑO DE LA ORGANIZACIÓN UTILIZANDO HERRAMIENTAS DE CALIDAD</t>
-  </si>
-  <si>
-    <t>PALOMINO</t>
-  </si>
-  <si>
-    <t>MELCHOR</t>
-  </si>
-  <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>CARLOS YAEL</t>
-  </si>
-  <si>
-    <t>JOSE RAUL</t>
-  </si>
-  <si>
-    <t>AARON MIGUEL</t>
-  </si>
-  <si>
-    <t>GEOVANNI</t>
-  </si>
-  <si>
-    <t>ALDAHIR</t>
-  </si>
-  <si>
-    <t>JORGE IVAN</t>
-  </si>
-  <si>
-    <t>DAMIAN</t>
-  </si>
-  <si>
-    <t>SALAS</t>
-  </si>
-  <si>
-    <t>MELISA VIANNEY</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>MOLOHUA</t>
-  </si>
-  <si>
-    <t>MIXCOHUA</t>
-  </si>
-  <si>
-    <t>AYLIN MELISSA</t>
-  </si>
-  <si>
-    <t>CRISTHIAN</t>
-  </si>
-  <si>
-    <t>CRISTIAN FERNANDO</t>
-  </si>
-  <si>
-    <t>YAHIR</t>
-  </si>
-  <si>
-    <t>CANDIDO</t>
-  </si>
-  <si>
-    <t>TEMAS DE FÍSICA</t>
-  </si>
-  <si>
-    <t>TEMAS DE FILOSOFÍA</t>
-  </si>
-  <si>
-    <t>PROBABILIDAD Y ESTADÍSTICA</t>
-  </si>
-  <si>
-    <t>BAEZ</t>
-  </si>
-  <si>
-    <t>GAEL JARED</t>
-  </si>
-  <si>
-    <t>JOSUE EDUARDO</t>
-  </si>
-  <si>
-    <t>NAHOMI ITZAYANA</t>
-  </si>
-  <si>
-    <t>MATEMÁTICAS APLICADAS</t>
-  </si>
-  <si>
-    <t>LIZBETH JOSELYN</t>
-  </si>
-  <si>
-    <t>INTRODUCCIÓN A LA ECONOMÍA</t>
-  </si>
-  <si>
-    <t>LORENZO</t>
-  </si>
-  <si>
-    <t>ARELLANO</t>
-  </si>
-  <si>
-    <t>NAVARRO</t>
-  </si>
-  <si>
-    <t>PIEDRAS</t>
-  </si>
-  <si>
-    <t>CUICAHUA</t>
-  </si>
-  <si>
-    <t>JORGE GUILLERMO</t>
-  </si>
-  <si>
-    <t>WENCESLAO</t>
-  </si>
-  <si>
-    <t>JORGE MARIO</t>
-  </si>
-  <si>
-    <t>LUIS REY</t>
-  </si>
-  <si>
-    <t>DARINKA</t>
-  </si>
-  <si>
-    <t>GREGORIO</t>
-  </si>
-  <si>
-    <t>ZUÑIGA</t>
-  </si>
-  <si>
-    <t>ZARATE</t>
-  </si>
-  <si>
-    <t>MONGE</t>
-  </si>
-  <si>
-    <t>ESPINDOLA</t>
-  </si>
-  <si>
-    <t>NAHOMY</t>
-  </si>
-  <si>
-    <t>JOSE RAFAEL</t>
-  </si>
-  <si>
-    <t>DIANA CRISTINA</t>
-  </si>
-  <si>
-    <t>DIEGO EMILIO</t>
-  </si>
-  <si>
-    <t>ROSA ITZEL</t>
-  </si>
-  <si>
-    <t>TEMAS DE BIOLOGÍA CONTEMPORÁNEA</t>
-  </si>
-  <si>
-    <t>BUSTOS</t>
-  </si>
-  <si>
-    <t>CERONIO</t>
-  </si>
-  <si>
-    <t>LARA</t>
-  </si>
-  <si>
-    <t>TEQUIHUATLE</t>
-  </si>
-  <si>
-    <t>COCOTLE</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>ANGEL CHARBEL</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>JOSE EMILIANO</t>
-  </si>
-  <si>
-    <t>JOSE ALDAIR</t>
-  </si>
-  <si>
-    <t>EMMANUEL</t>
-  </si>
-  <si>
-    <t>KEVYN DANIEL</t>
-  </si>
-  <si>
-    <t>ROBBIE ALONSO</t>
-  </si>
-  <si>
-    <t>ANTHONY</t>
-  </si>
-  <si>
-    <t>ISAAC</t>
   </si>
   <si>
     <t>ALMANZA</t>
@@ -2376,16 +2385,16 @@
         <v>21330051920053</v>
       </c>
       <c r="B2" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="C2" t="s">
         <v>105</v>
       </c>
       <c r="D2" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="E2" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -2396,16 +2405,16 @@
         <v>21330051920053</v>
       </c>
       <c r="B3" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="C3" t="s">
         <v>105</v>
       </c>
       <c r="D3" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="E3" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -2422,10 +2431,10 @@
         <v>23</v>
       </c>
       <c r="D4" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="E4" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -2442,10 +2451,10 @@
         <v>23</v>
       </c>
       <c r="D5" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="E5" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -2456,16 +2465,16 @@
         <v>21330051920242</v>
       </c>
       <c r="B6" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="C6" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="D6" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="E6" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -2476,16 +2485,16 @@
         <v>21330051920242</v>
       </c>
       <c r="B7" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="C7" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="D7" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="E7" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -2496,16 +2505,16 @@
         <v>21330051920359</v>
       </c>
       <c r="B8" t="s">
-        <v>233</v>
+        <v>155</v>
       </c>
       <c r="C8" t="s">
         <v>105</v>
       </c>
       <c r="D8" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="E8" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -2516,16 +2525,16 @@
         <v>22330051920054</v>
       </c>
       <c r="B9" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="C9" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="D9" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E9" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -2539,13 +2548,13 @@
         <v>17</v>
       </c>
       <c r="C10" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="D10" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="E10" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -2562,10 +2571,10 @@
         <v>6</v>
       </c>
       <c r="D11" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="E11" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -2579,13 +2588,13 @@
         <v>23</v>
       </c>
       <c r="C12" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="D12" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="E12" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -2599,13 +2608,13 @@
         <v>23</v>
       </c>
       <c r="C13" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="D13" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="E13" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -2616,16 +2625,16 @@
         <v>22330051920068</v>
       </c>
       <c r="B14" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="C14" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="D14" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="E14" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="F14">
         <v>5</v>
@@ -2636,16 +2645,16 @@
         <v>22330051920068</v>
       </c>
       <c r="B15" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="C15" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="D15" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="E15" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="F15">
         <v>5</v>
@@ -2659,13 +2668,13 @@
         <v>54</v>
       </c>
       <c r="C16" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D16" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="E16" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="F16">
         <v>5</v>
@@ -2679,13 +2688,13 @@
         <v>54</v>
       </c>
       <c r="C17" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D17" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="E17" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="F17">
         <v>5</v>
@@ -2699,13 +2708,13 @@
         <v>46</v>
       </c>
       <c r="C18" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="D18" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="E18" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="F18">
         <v>5</v>
@@ -2719,13 +2728,13 @@
         <v>46</v>
       </c>
       <c r="C19" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="D19" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="E19" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="F19">
         <v>5</v>
@@ -2736,16 +2745,16 @@
         <v>22330051920317</v>
       </c>
       <c r="B20" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="C20" t="s">
         <v>54</v>
       </c>
       <c r="D20" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="E20" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="F20">
         <v>5</v>
@@ -2756,16 +2765,16 @@
         <v>22330051920425</v>
       </c>
       <c r="B21" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C21" t="s">
         <v>23</v>
       </c>
       <c r="D21" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="E21" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="F21">
         <v>5</v>
@@ -2812,10 +2821,10 @@
         <v>102</v>
       </c>
       <c r="D2" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="E2" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -2832,10 +2841,10 @@
         <v>102</v>
       </c>
       <c r="D3" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="E3" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -2846,16 +2855,16 @@
         <v>22330051920036</v>
       </c>
       <c r="B4" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="C4" t="s">
         <v>14</v>
       </c>
       <c r="D4" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="E4" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -2866,16 +2875,16 @@
         <v>22330051920043</v>
       </c>
       <c r="B5" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C5" t="s">
         <v>23</v>
       </c>
       <c r="D5" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="E5" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -2886,16 +2895,16 @@
         <v>22330051920043</v>
       </c>
       <c r="B6" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C6" t="s">
         <v>23</v>
       </c>
       <c r="D6" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="E6" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -2912,10 +2921,10 @@
         <v>21</v>
       </c>
       <c r="D7" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E7" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -2926,16 +2935,16 @@
         <v>22330051920191</v>
       </c>
       <c r="B8" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="C8" t="s">
         <v>115</v>
       </c>
       <c r="D8" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="E8" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -2949,13 +2958,13 @@
         <v>48</v>
       </c>
       <c r="C9" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="D9" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="E9" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -2969,13 +2978,13 @@
         <v>23</v>
       </c>
       <c r="C10" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="D10" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="E10" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -3016,16 +3025,16 @@
         <v>22330051920145</v>
       </c>
       <c r="B2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="C2" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="D2" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="E2" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -3069,13 +3078,13 @@
         <v>61</v>
       </c>
       <c r="C2" t="s">
-        <v>233</v>
+        <v>155</v>
       </c>
       <c r="D2" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="E2" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -3092,10 +3101,10 @@
         <v>40</v>
       </c>
       <c r="D3" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="E3" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -3106,16 +3115,16 @@
         <v>21330051920153</v>
       </c>
       <c r="B4" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="C4" t="s">
         <v>21</v>
       </c>
       <c r="D4" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="E4" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -3126,16 +3135,16 @@
         <v>21330051920153</v>
       </c>
       <c r="B5" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="C5" t="s">
         <v>21</v>
       </c>
       <c r="D5" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="E5" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -3146,16 +3155,16 @@
         <v>21330051920162</v>
       </c>
       <c r="B6" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="C6" t="s">
         <v>23</v>
       </c>
       <c r="D6" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="E6" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -3166,16 +3175,16 @@
         <v>21330051920171</v>
       </c>
       <c r="B7" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C7" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="D7" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="E7" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -3186,16 +3195,16 @@
         <v>21330051920171</v>
       </c>
       <c r="B8" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C8" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="D8" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="E8" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -3206,16 +3215,16 @@
         <v>21330051920176</v>
       </c>
       <c r="B9" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C9" t="s">
         <v>108</v>
       </c>
       <c r="D9" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="E9" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -3226,16 +3235,16 @@
         <v>21330051920176</v>
       </c>
       <c r="B10" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C10" t="s">
         <v>108</v>
       </c>
       <c r="D10" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="E10" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -3306,16 +3315,16 @@
         <v>21330051920137</v>
       </c>
       <c r="B2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C2" t="s">
-        <v>233</v>
+        <v>155</v>
       </c>
       <c r="D2" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="E2" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -3326,16 +3335,16 @@
         <v>21330051920334</v>
       </c>
       <c r="B3" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="C3" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="D3" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="E3" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -3346,16 +3355,16 @@
         <v>21330051920334</v>
       </c>
       <c r="B4" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="C4" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="D4" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="E4" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -3366,16 +3375,16 @@
         <v>21330051920335</v>
       </c>
       <c r="B5" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="C5" t="s">
         <v>69</v>
       </c>
       <c r="D5" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="E5" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -3416,16 +3425,16 @@
         <v>21330051920235</v>
       </c>
       <c r="B2" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="C2" t="s">
         <v>42</v>
       </c>
       <c r="D2" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="E2" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -3466,16 +3475,16 @@
         <v>21330051920190</v>
       </c>
       <c r="B2" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="C2" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="D2" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="E2" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -3486,16 +3495,16 @@
         <v>21330051920190</v>
       </c>
       <c r="B3" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="C3" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="D3" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="E3" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -3509,13 +3518,13 @@
         <v>46</v>
       </c>
       <c r="C4" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="D4" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="E4" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -3526,16 +3535,16 @@
         <v>21330051920209</v>
       </c>
       <c r="B5" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C5" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="D5" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="E5" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -3546,16 +3555,16 @@
         <v>21330051920209</v>
       </c>
       <c r="B6" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C6" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="D6" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="E6" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -3566,16 +3575,16 @@
         <v>21330051920212</v>
       </c>
       <c r="B7" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="C7" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="D7" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="E7" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -3589,13 +3598,13 @@
         <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="D8" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="E8" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -3606,16 +3615,16 @@
         <v>21330051920386</v>
       </c>
       <c r="B9" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="C9" t="s">
-        <v>233</v>
+        <v>155</v>
       </c>
       <c r="D9" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="E9" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -3626,16 +3635,16 @@
         <v>21330051920386</v>
       </c>
       <c r="B10" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="C10" t="s">
-        <v>233</v>
+        <v>155</v>
       </c>
       <c r="D10" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="E10" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -3676,16 +3685,16 @@
         <v>19330051920208</v>
       </c>
       <c r="B2" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="C2" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="D2" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="E2" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -3696,16 +3705,16 @@
         <v>20330051920235</v>
       </c>
       <c r="B3" t="s">
-        <v>233</v>
+        <v>155</v>
       </c>
       <c r="C3" t="s">
         <v>14</v>
       </c>
       <c r="D3" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="E3" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -3716,16 +3725,16 @@
         <v>20330051920235</v>
       </c>
       <c r="B4" t="s">
-        <v>233</v>
+        <v>155</v>
       </c>
       <c r="C4" t="s">
         <v>14</v>
       </c>
       <c r="D4" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="E4" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -3745,7 +3754,7 @@
         <v>138</v>
       </c>
       <c r="E5" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -3759,13 +3768,13 @@
         <v>105</v>
       </c>
       <c r="C6" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="D6" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="E6" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -3779,13 +3788,13 @@
         <v>105</v>
       </c>
       <c r="C7" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="D7" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="E7" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -3799,13 +3808,13 @@
         <v>106</v>
       </c>
       <c r="C8" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="D8" t="s">
         <v>34</v>
       </c>
       <c r="E8" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -3816,16 +3825,16 @@
         <v>21330051920323</v>
       </c>
       <c r="B9" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="C9" t="s">
         <v>14</v>
       </c>
       <c r="D9" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="E9" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -3836,16 +3845,16 @@
         <v>21330051920323</v>
       </c>
       <c r="B10" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="C10" t="s">
         <v>14</v>
       </c>
       <c r="D10" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="E10" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -3856,16 +3865,16 @@
         <v>21330051920330</v>
       </c>
       <c r="B11" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="C11" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="D11" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="E11" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -3876,16 +3885,16 @@
         <v>21330051920330</v>
       </c>
       <c r="B12" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="C12" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="D12" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="E12" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -3929,10 +3938,10 @@
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D2" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="E2" t="s">
         <v>36</v>
@@ -3949,10 +3958,10 @@
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D3" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="E3" t="s">
         <v>37</v>
@@ -3969,10 +3978,10 @@
         <v>6</v>
       </c>
       <c r="C4" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="D4" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="E4" t="s">
         <v>36</v>
@@ -3986,13 +3995,13 @@
         <v>23330051920180</v>
       </c>
       <c r="B5" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C5" t="s">
         <v>23</v>
       </c>
       <c r="D5" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="E5" t="s">
         <v>36</v>
@@ -4006,13 +4015,13 @@
         <v>23330051920182</v>
       </c>
       <c r="B6" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="C6" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D6" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="E6" t="s">
         <v>36</v>
@@ -4029,13 +4038,13 @@
         <v>42</v>
       </c>
       <c r="C7" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="D7" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="E7" t="s">
-        <v>276</v>
+        <v>410</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -4049,10 +4058,10 @@
         <v>42</v>
       </c>
       <c r="C8" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="D8" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="E8" t="s">
         <v>36</v>
@@ -4072,7 +4081,7 @@
         <v>20</v>
       </c>
       <c r="D9" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="E9" t="s">
         <v>36</v>
@@ -4089,16 +4098,16 @@
         <v>17</v>
       </c>
       <c r="C10" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="D10" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="E10" t="s">
-        <v>95</v>
+        <v>36</v>
       </c>
       <c r="F10">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -4109,16 +4118,16 @@
         <v>17</v>
       </c>
       <c r="C11" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="D11" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="E11" t="s">
-        <v>36</v>
+        <v>95</v>
       </c>
       <c r="F11">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -4126,13 +4135,13 @@
         <v>23330051920199</v>
       </c>
       <c r="B12" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C12" t="s">
         <v>46</v>
       </c>
       <c r="D12" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="E12" t="s">
         <v>36</v>
@@ -4149,10 +4158,10 @@
         <v>48</v>
       </c>
       <c r="C13" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="D13" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="E13" t="s">
         <v>36</v>
@@ -4166,13 +4175,13 @@
         <v>23330051920206</v>
       </c>
       <c r="B14" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="C14" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="D14" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="E14" t="s">
         <v>36</v>
@@ -4186,13 +4195,13 @@
         <v>23330051920210</v>
       </c>
       <c r="B15" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="C15" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="D15" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="E15" t="s">
         <v>36</v>
@@ -4625,10 +4634,10 @@
         <v>88</v>
       </c>
       <c r="E21" t="s">
-        <v>36</v>
+        <v>95</v>
       </c>
       <c r="F21">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -4645,10 +4654,10 @@
         <v>88</v>
       </c>
       <c r="E22" t="s">
-        <v>95</v>
+        <v>36</v>
       </c>
       <c r="F22">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -4812,7 +4821,7 @@
         <v>51</v>
       </c>
       <c r="D2" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="E2" t="s">
         <v>36</v>
@@ -4826,19 +4835,19 @@
         <v>23330051920218</v>
       </c>
       <c r="B3" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="C3" t="s">
         <v>15</v>
       </c>
       <c r="D3" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="E3" t="s">
-        <v>276</v>
+        <v>36</v>
       </c>
       <c r="F3">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -4846,19 +4855,19 @@
         <v>23330051920218</v>
       </c>
       <c r="B4" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="C4" t="s">
         <v>15</v>
       </c>
       <c r="D4" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="E4" t="s">
-        <v>36</v>
+        <v>410</v>
       </c>
       <c r="F4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -4872,7 +4881,7 @@
         <v>40</v>
       </c>
       <c r="D5" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="E5" t="s">
         <v>36</v>
@@ -4886,13 +4895,13 @@
         <v>23330051920223</v>
       </c>
       <c r="B6" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="C6" t="s">
-        <v>193</v>
+        <v>143</v>
       </c>
       <c r="D6" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="E6" t="s">
         <v>36</v>
@@ -4912,7 +4921,7 @@
         <v>15</v>
       </c>
       <c r="D7" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="E7" t="s">
         <v>37</v>
@@ -4932,7 +4941,7 @@
         <v>15</v>
       </c>
       <c r="D8" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="E8" t="s">
         <v>36</v>
@@ -4946,13 +4955,13 @@
         <v>23330051920247</v>
       </c>
       <c r="B9" t="s">
-        <v>233</v>
+        <v>155</v>
       </c>
       <c r="C9" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="D9" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="E9" t="s">
         <v>37</v>
@@ -4966,13 +4975,13 @@
         <v>23330051920247</v>
       </c>
       <c r="B10" t="s">
-        <v>233</v>
+        <v>155</v>
       </c>
       <c r="C10" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="D10" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="E10" t="s">
         <v>36</v>
@@ -4992,13 +5001,13 @@
         <v>100</v>
       </c>
       <c r="D11" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E11" t="s">
-        <v>36</v>
+        <v>410</v>
       </c>
       <c r="F11">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -5012,13 +5021,13 @@
         <v>100</v>
       </c>
       <c r="D12" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E12" t="s">
-        <v>276</v>
+        <v>36</v>
       </c>
       <c r="F12">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -5029,16 +5038,16 @@
         <v>14</v>
       </c>
       <c r="C13" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="D13" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="E13" t="s">
-        <v>36</v>
+        <v>410</v>
       </c>
       <c r="F13">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -5049,16 +5058,16 @@
         <v>14</v>
       </c>
       <c r="C14" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="D14" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="E14" t="s">
-        <v>276</v>
+        <v>36</v>
       </c>
       <c r="F14">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -5072,7 +5081,7 @@
         <v>65</v>
       </c>
       <c r="D15" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="E15" t="s">
         <v>36</v>
@@ -5116,13 +5125,13 @@
         <v>23330051920281</v>
       </c>
       <c r="B2" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="C2" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="D2" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="E2" t="s">
         <v>36</v>
@@ -5136,13 +5145,13 @@
         <v>23330051920284</v>
       </c>
       <c r="B3" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="C3" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="D3" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="E3" t="s">
         <v>36</v>
@@ -5156,13 +5165,13 @@
         <v>23330051920285</v>
       </c>
       <c r="B4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C4" t="s">
         <v>48</v>
       </c>
       <c r="D4" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="E4" t="s">
         <v>36</v>
@@ -5196,13 +5205,13 @@
         <v>23330051920295</v>
       </c>
       <c r="B6" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="C6" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="D6" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="E6" t="s">
         <v>36</v>
@@ -5216,13 +5225,13 @@
         <v>23330051920296</v>
       </c>
       <c r="B7" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="C7" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D7" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="E7" t="s">
         <v>36</v>
@@ -5236,13 +5245,13 @@
         <v>23330051920299</v>
       </c>
       <c r="B8" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C8" t="s">
         <v>23</v>
       </c>
       <c r="D8" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="E8" t="s">
         <v>36</v>
@@ -5259,10 +5268,10 @@
         <v>101</v>
       </c>
       <c r="C9" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D9" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="E9" t="s">
         <v>36</v>
@@ -5276,16 +5285,16 @@
         <v>23330051920308</v>
       </c>
       <c r="B10" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C10" t="s">
         <v>14</v>
       </c>
       <c r="D10" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="E10" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -5296,13 +5305,13 @@
         <v>23330051920308</v>
       </c>
       <c r="B11" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C11" t="s">
         <v>14</v>
       </c>
       <c r="D11" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="E11" t="s">
         <v>36</v>
@@ -5316,13 +5325,13 @@
         <v>23330051920322</v>
       </c>
       <c r="B12" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="C12" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="D12" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="E12" t="s">
         <v>36</v>
@@ -5336,13 +5345,13 @@
         <v>23330051920326</v>
       </c>
       <c r="B13" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C13" t="s">
         <v>19</v>
       </c>
       <c r="D13" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="E13" t="s">
         <v>36</v>
@@ -5359,10 +5368,10 @@
         <v>109</v>
       </c>
       <c r="C14" t="s">
-        <v>233</v>
+        <v>155</v>
       </c>
       <c r="D14" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="E14" t="s">
         <v>36</v>
@@ -5376,13 +5385,13 @@
         <v>23330051920363</v>
       </c>
       <c r="B15" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="C15" t="s">
         <v>105</v>
       </c>
       <c r="D15" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="E15" t="s">
         <v>36</v>
@@ -5426,13 +5435,13 @@
         <v>23330051920207</v>
       </c>
       <c r="B2" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="C2" t="s">
         <v>17</v>
       </c>
       <c r="D2" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="E2" t="s">
         <v>36</v>
@@ -5446,13 +5455,13 @@
         <v>23330051920213</v>
       </c>
       <c r="B3" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="C3" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="D3" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="E3" t="s">
         <v>36</v>
@@ -5466,19 +5475,19 @@
         <v>23330051920226</v>
       </c>
       <c r="B4" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="C4" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="D4" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="E4" t="s">
-        <v>277</v>
+        <v>36</v>
       </c>
       <c r="F4">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -5486,19 +5495,19 @@
         <v>23330051920226</v>
       </c>
       <c r="B5" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="C5" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="D5" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="E5" t="s">
-        <v>36</v>
+        <v>183</v>
       </c>
       <c r="F5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -5506,13 +5515,13 @@
         <v>23330051920227</v>
       </c>
       <c r="B6" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="C6" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="D6" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="E6" t="s">
         <v>36</v>
@@ -5526,13 +5535,13 @@
         <v>23330051920239</v>
       </c>
       <c r="B7" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="C7" t="s">
         <v>49</v>
       </c>
       <c r="D7" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="E7" t="s">
         <v>36</v>
@@ -5546,13 +5555,13 @@
         <v>23330051920240</v>
       </c>
       <c r="B8" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="C8" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D8" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="E8" t="s">
         <v>36</v>
@@ -5566,13 +5575,13 @@
         <v>23330051920242</v>
       </c>
       <c r="B9" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="C9" t="s">
         <v>24</v>
       </c>
       <c r="D9" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="E9" t="s">
         <v>36</v>
@@ -5586,16 +5595,16 @@
         <v>23330051920244</v>
       </c>
       <c r="B10" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C10" t="s">
         <v>14</v>
       </c>
       <c r="D10" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="E10" t="s">
-        <v>277</v>
+        <v>183</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -5606,13 +5615,13 @@
         <v>23330051920244</v>
       </c>
       <c r="B11" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C11" t="s">
         <v>14</v>
       </c>
       <c r="D11" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="E11" t="s">
         <v>36</v>
@@ -5629,10 +5638,10 @@
         <v>105</v>
       </c>
       <c r="C12" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="D12" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="E12" t="s">
         <v>36</v>
@@ -5646,13 +5655,13 @@
         <v>23330051920257</v>
       </c>
       <c r="B13" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="C13" t="s">
-        <v>279</v>
+        <v>218</v>
       </c>
       <c r="D13" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="E13" t="s">
         <v>36</v>
@@ -5666,13 +5675,13 @@
         <v>23330051920260</v>
       </c>
       <c r="B14" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="C14" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="D14" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E14" t="s">
         <v>36</v>
@@ -5686,7 +5695,7 @@
         <v>23330051920270</v>
       </c>
       <c r="B15" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="C15" t="s">
         <v>11</v>
@@ -5712,7 +5721,7 @@
         <v>23</v>
       </c>
       <c r="D16" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="E16" t="s">
         <v>36</v>
@@ -5726,13 +5735,13 @@
         <v>23330051920328</v>
       </c>
       <c r="B17" t="s">
-        <v>233</v>
+        <v>155</v>
       </c>
       <c r="C17" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="D17" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="E17" t="s">
         <v>36</v>
@@ -5752,7 +5761,7 @@
         <v>23</v>
       </c>
       <c r="D18" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="E18" t="s">
         <v>36</v>
@@ -5772,7 +5781,7 @@
         <v>105</v>
       </c>
       <c r="D19" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="E19" t="s">
         <v>36</v>
@@ -5792,10 +5801,10 @@
         <v>105</v>
       </c>
       <c r="D20" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="E20" t="s">
-        <v>277</v>
+        <v>183</v>
       </c>
       <c r="F20">
         <v>5</v>
@@ -5836,13 +5845,13 @@
         <v>23330051920287</v>
       </c>
       <c r="B2" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="C2" t="s">
         <v>14</v>
       </c>
       <c r="D2" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="E2" t="s">
         <v>36</v>
@@ -5856,13 +5865,13 @@
         <v>23330051920288</v>
       </c>
       <c r="B3" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="C3" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="D3" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="E3" t="s">
         <v>36</v>
@@ -5879,16 +5888,16 @@
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="D4" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="E4" t="s">
-        <v>36</v>
+        <v>410</v>
       </c>
       <c r="F4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -5899,16 +5908,16 @@
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="D5" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="E5" t="s">
-        <v>276</v>
+        <v>36</v>
       </c>
       <c r="F5">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -5919,10 +5928,10 @@
         <v>46</v>
       </c>
       <c r="C6" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="D6" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="E6" t="s">
         <v>36</v>
@@ -5939,7 +5948,7 @@
         <v>62</v>
       </c>
       <c r="C7" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="D7" t="s">
         <v>70</v>
@@ -5986,16 +5995,16 @@
         <v>21330051920007</v>
       </c>
       <c r="B2" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="C2" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="D2" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="E2" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -6006,16 +6015,16 @@
         <v>22330051920177</v>
       </c>
       <c r="B3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C3" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="D3" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="E3" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -6026,16 +6035,16 @@
         <v>22330051920177</v>
       </c>
       <c r="B4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C4" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="D4" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="E4" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -6049,13 +6058,13 @@
         <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D5" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="E5" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -6069,13 +6078,13 @@
         <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D6" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="E6" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -6089,13 +6098,13 @@
         <v>13</v>
       </c>
       <c r="C7" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="D7" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="E7" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -6106,16 +6115,16 @@
         <v>22330051920192</v>
       </c>
       <c r="B8" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C8" t="s">
         <v>23</v>
       </c>
       <c r="D8" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="E8" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -6126,16 +6135,16 @@
         <v>22330051920192</v>
       </c>
       <c r="B9" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C9" t="s">
         <v>23</v>
       </c>
       <c r="D9" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="E9" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -6149,13 +6158,13 @@
         <v>100</v>
       </c>
       <c r="C10" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="D10" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="E10" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -6169,13 +6178,13 @@
         <v>100</v>
       </c>
       <c r="C11" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="D11" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="E11" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -6192,10 +6201,10 @@
         <v>41</v>
       </c>
       <c r="D12" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="E12" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -6212,10 +6221,10 @@
         <v>41</v>
       </c>
       <c r="D13" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="E13" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -6229,13 +6238,13 @@
         <v>55</v>
       </c>
       <c r="C14" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="D14" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="E14" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="F14">
         <v>5</v>
@@ -6249,13 +6258,13 @@
         <v>55</v>
       </c>
       <c r="C15" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="D15" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="E15" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="F15">
         <v>5</v>
@@ -6269,13 +6278,13 @@
         <v>105</v>
       </c>
       <c r="C16" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="D16" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="E16" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="F16">
         <v>5</v>
@@ -6286,16 +6295,16 @@
         <v>22330051920413</v>
       </c>
       <c r="B17" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="C17" t="s">
         <v>6</v>
       </c>
       <c r="D17" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="E17" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="F17">
         <v>5</v>
@@ -6336,16 +6345,16 @@
         <v>22330051920230</v>
       </c>
       <c r="B2" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="C2" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="D2" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="E2" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -6356,16 +6365,16 @@
         <v>22330051920235</v>
       </c>
       <c r="B3" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="C3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D3" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="E3" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -6376,16 +6385,16 @@
         <v>22330051920235</v>
       </c>
       <c r="B4" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="C4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D4" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="E4" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -6396,16 +6405,16 @@
         <v>22330051920253</v>
       </c>
       <c r="B5" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C5" t="s">
-        <v>233</v>
+        <v>155</v>
       </c>
       <c r="D5" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="E5" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -6422,10 +6431,10 @@
         <v>115</v>
       </c>
       <c r="D6" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="E6" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -6442,10 +6451,10 @@
         <v>115</v>
       </c>
       <c r="D7" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="E7" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -6459,13 +6468,13 @@
         <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="D8" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="E8" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -6476,16 +6485,16 @@
         <v>22330051920401</v>
       </c>
       <c r="B9" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="C9" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="D9" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="E9" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -6526,16 +6535,16 @@
         <v>21330051920117</v>
       </c>
       <c r="B2" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="C2" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="D2" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="E2" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -6546,16 +6555,16 @@
         <v>21330051920117</v>
       </c>
       <c r="B3" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="C3" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="D3" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="E3" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -6569,13 +6578,13 @@
         <v>69</v>
       </c>
       <c r="C4" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="D4" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="E4" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -6586,16 +6595,16 @@
         <v>22330051920402</v>
       </c>
       <c r="B5" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C5" t="s">
         <v>23</v>
       </c>
       <c r="D5" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="E5" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -6639,13 +6648,13 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="D2" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="E2" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -6692,10 +6701,10 @@
         <v>105</v>
       </c>
       <c r="D2" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="E2" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -6706,16 +6715,16 @@
         <v>22330051920312</v>
       </c>
       <c r="B3" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="C3" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="D3" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="E3" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -6732,10 +6741,10 @@
         <v>65</v>
       </c>
       <c r="D4" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="E4" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -6752,10 +6761,10 @@
         <v>65</v>
       </c>
       <c r="D5" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="E5" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -6772,10 +6781,10 @@
         <v>23</v>
       </c>
       <c r="D6" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="E6" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -6792,10 +6801,10 @@
         <v>23</v>
       </c>
       <c r="D7" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="E7" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -6812,10 +6821,10 @@
         <v>109</v>
       </c>
       <c r="D8" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="E8" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -6856,16 +6865,16 @@
         <v>20330051920022</v>
       </c>
       <c r="B2" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="C2" t="s">
         <v>16</v>
       </c>
       <c r="D2" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="E2" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -6882,10 +6891,10 @@
         <v>10</v>
       </c>
       <c r="D3" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="E3" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -6896,16 +6905,16 @@
         <v>21330051920003</v>
       </c>
       <c r="B4" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="C4" t="s">
         <v>24</v>
       </c>
       <c r="D4" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="E4" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -6919,13 +6928,13 @@
         <v>10</v>
       </c>
       <c r="C5" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="D5" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="E5" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -6942,10 +6951,10 @@
         <v>115</v>
       </c>
       <c r="D6" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="E6" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -6956,16 +6965,16 @@
         <v>21330051920021</v>
       </c>
       <c r="B7" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="C7" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="D7" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="E7" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -6976,16 +6985,16 @@
         <v>21330051920021</v>
       </c>
       <c r="B8" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="C8" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="D8" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="E8" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -6996,16 +7005,16 @@
         <v>21330051920022</v>
       </c>
       <c r="B9" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="C9" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="D9" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="E9" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -7016,16 +7025,16 @@
         <v>21330051920022</v>
       </c>
       <c r="B10" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="C10" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="D10" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="E10" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -7036,16 +7045,16 @@
         <v>21330051920023</v>
       </c>
       <c r="B11" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="C11" t="s">
         <v>11</v>
       </c>
       <c r="D11" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="E11" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -7056,16 +7065,16 @@
         <v>21330051920023</v>
       </c>
       <c r="B12" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="C12" t="s">
         <v>11</v>
       </c>
       <c r="D12" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="E12" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -7076,16 +7085,16 @@
         <v>21330051920028</v>
       </c>
       <c r="B13" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="C13" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="D13" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="E13" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -7102,10 +7111,10 @@
         <v>14</v>
       </c>
       <c r="D14" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="E14" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="F14">
         <v>5</v>
@@ -7122,10 +7131,10 @@
         <v>14</v>
       </c>
       <c r="D15" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="E15" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="F15">
         <v>5</v>
@@ -7315,10 +7324,10 @@
         <v>124</v>
       </c>
       <c r="E9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F9">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -7335,10 +7344,10 @@
         <v>124</v>
       </c>
       <c r="E10" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F10">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -7355,10 +7364,10 @@
         <v>125</v>
       </c>
       <c r="E11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F11">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -7375,10 +7384,10 @@
         <v>125</v>
       </c>
       <c r="E12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F12">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -7415,10 +7424,10 @@
         <v>127</v>
       </c>
       <c r="E14" t="s">
-        <v>137</v>
+        <v>36</v>
       </c>
       <c r="F14">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -7435,10 +7444,10 @@
         <v>127</v>
       </c>
       <c r="E15" t="s">
-        <v>36</v>
+        <v>137</v>
       </c>
       <c r="F15">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -7679,13 +7688,13 @@
         <v>42</v>
       </c>
       <c r="C2" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="D2" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="E2" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -7696,16 +7705,16 @@
         <v>21330051920100</v>
       </c>
       <c r="B3" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C3" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="D3" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="E3" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -7722,10 +7731,10 @@
         <v>42</v>
       </c>
       <c r="D4" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="E4" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -7736,16 +7745,16 @@
         <v>21330051920107</v>
       </c>
       <c r="B5" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="C5" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="D5" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="E5" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -7756,16 +7765,16 @@
         <v>21330051920107</v>
       </c>
       <c r="B6" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="C6" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="D6" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="E6" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -7812,10 +7821,10 @@
         <v>17</v>
       </c>
       <c r="D2" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="E2" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -7832,10 +7841,10 @@
         <v>10</v>
       </c>
       <c r="D3" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="E3" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -7852,10 +7861,10 @@
         <v>10</v>
       </c>
       <c r="D4" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="E4" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -7896,16 +7905,16 @@
         <v>20330051920132</v>
       </c>
       <c r="B2" t="s">
-        <v>233</v>
+        <v>155</v>
       </c>
       <c r="C2" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="D2" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="E2" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -7916,16 +7925,16 @@
         <v>20330051920132</v>
       </c>
       <c r="B3" t="s">
-        <v>233</v>
+        <v>155</v>
       </c>
       <c r="C3" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="D3" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="E3" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -7936,16 +7945,16 @@
         <v>21330051920031</v>
       </c>
       <c r="B4" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="C4" t="s">
         <v>69</v>
       </c>
       <c r="D4" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="E4" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -7956,16 +7965,16 @@
         <v>21330051920031</v>
       </c>
       <c r="B5" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="C5" t="s">
         <v>69</v>
       </c>
       <c r="D5" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="E5" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -7979,13 +7988,13 @@
         <v>11</v>
       </c>
       <c r="C6" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="D6" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="E6" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -7999,13 +8008,13 @@
         <v>98</v>
       </c>
       <c r="C7" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="D7" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="E7" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -8019,13 +8028,13 @@
         <v>98</v>
       </c>
       <c r="C8" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="D8" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="E8" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -8039,13 +8048,13 @@
         <v>61</v>
       </c>
       <c r="C9" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="D9" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="E9" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -8059,13 +8068,13 @@
         <v>10</v>
       </c>
       <c r="C10" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="D10" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="E10" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -8079,13 +8088,13 @@
         <v>10</v>
       </c>
       <c r="C11" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="D11" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="E11" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -8129,13 +8138,13 @@
         <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="D2" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="E2" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -8148,7 +8157,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F43"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -8179,10 +8188,10 @@
         <v>138</v>
       </c>
       <c r="C2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="E2" t="s">
         <v>36</v>
@@ -8193,19 +8202,19 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>23330051920048</v>
+        <v>23330051920050</v>
       </c>
       <c r="B3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C3" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D3" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="E3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F3">
         <v>-1</v>
@@ -8213,16 +8222,16 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>23330051920050</v>
+        <v>23330051920053</v>
       </c>
       <c r="B4" t="s">
-        <v>139</v>
+        <v>41</v>
       </c>
       <c r="C4" t="s">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="D4" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="E4" t="s">
         <v>36</v>
@@ -8233,19 +8242,19 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>23330051920050</v>
+        <v>23330051920054</v>
       </c>
       <c r="B5" t="s">
-        <v>139</v>
+        <v>113</v>
       </c>
       <c r="C5" t="s">
-        <v>150</v>
+        <v>20</v>
       </c>
       <c r="D5" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="E5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F5">
         <v>-1</v>
@@ -8253,16 +8262,16 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>23330051920053</v>
+        <v>23330051920055</v>
       </c>
       <c r="B6" t="s">
-        <v>41</v>
+        <v>115</v>
       </c>
       <c r="C6" t="s">
-        <v>60</v>
+        <v>152</v>
       </c>
       <c r="D6" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="E6" t="s">
         <v>36</v>
@@ -8273,19 +8282,19 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>23330051920053</v>
+        <v>23330051920056</v>
       </c>
       <c r="B7" t="s">
-        <v>41</v>
+        <v>140</v>
       </c>
       <c r="C7" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="D7" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="E7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F7">
         <v>-1</v>
@@ -8293,16 +8302,16 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>23330051920054</v>
+        <v>23330051920057</v>
       </c>
       <c r="B8" t="s">
-        <v>113</v>
+        <v>140</v>
       </c>
       <c r="C8" t="s">
-        <v>20</v>
+        <v>105</v>
       </c>
       <c r="D8" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="E8" t="s">
         <v>36</v>
@@ -8313,19 +8322,19 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>23330051920054</v>
+        <v>23330051920058</v>
       </c>
       <c r="B9" t="s">
-        <v>113</v>
+        <v>59</v>
       </c>
       <c r="C9" t="s">
-        <v>20</v>
+        <v>153</v>
       </c>
       <c r="D9" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="E9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F9">
         <v>-1</v>
@@ -8333,19 +8342,19 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>23330051920055</v>
+        <v>23330051920060</v>
       </c>
       <c r="B10" t="s">
-        <v>115</v>
+        <v>141</v>
       </c>
       <c r="C10" t="s">
-        <v>151</v>
+        <v>23</v>
       </c>
       <c r="D10" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="E10" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F10">
         <v>-1</v>
@@ -8353,16 +8362,16 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>23330051920055</v>
+        <v>23330051920061</v>
       </c>
       <c r="B11" t="s">
-        <v>115</v>
+        <v>142</v>
       </c>
       <c r="C11" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="D11" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="E11" t="s">
         <v>36</v>
@@ -8373,16 +8382,16 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>23330051920056</v>
+        <v>23330051920062</v>
       </c>
       <c r="B12" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="C12" t="s">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="D12" t="s">
-        <v>165</v>
+        <v>86</v>
       </c>
       <c r="E12" t="s">
         <v>36</v>
@@ -8393,39 +8402,39 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>23330051920056</v>
+        <v>23330051920062</v>
       </c>
       <c r="B13" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="C13" t="s">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="D13" t="s">
-        <v>165</v>
+        <v>86</v>
       </c>
       <c r="E13" t="s">
-        <v>37</v>
+        <v>137</v>
       </c>
       <c r="F13">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>23330051920057</v>
+        <v>23330051920063</v>
       </c>
       <c r="B14" t="s">
-        <v>140</v>
+        <v>105</v>
       </c>
       <c r="C14" t="s">
-        <v>105</v>
+        <v>11</v>
       </c>
       <c r="D14" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="E14" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F14">
         <v>-1</v>
@@ -8433,16 +8442,16 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>23330051920057</v>
+        <v>23330051920064</v>
       </c>
       <c r="B15" t="s">
-        <v>140</v>
+        <v>105</v>
       </c>
       <c r="C15" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D15" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="E15" t="s">
         <v>36</v>
@@ -8453,36 +8462,36 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>23330051920058</v>
+        <v>23330051920065</v>
       </c>
       <c r="B16" t="s">
-        <v>59</v>
+        <v>19</v>
       </c>
       <c r="C16" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="D16" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="E16" t="s">
-        <v>37</v>
+        <v>183</v>
       </c>
       <c r="F16">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>23330051920058</v>
+        <v>23330051920065</v>
       </c>
       <c r="B17" t="s">
-        <v>59</v>
+        <v>19</v>
       </c>
       <c r="C17" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="D17" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="E17" t="s">
         <v>36</v>
@@ -8493,16 +8502,16 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18">
-        <v>23330051920060</v>
+        <v>23330051920066</v>
       </c>
       <c r="B18" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="C18" t="s">
-        <v>23</v>
+        <v>111</v>
       </c>
       <c r="D18" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="E18" t="s">
         <v>36</v>
@@ -8513,19 +8522,19 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19">
-        <v>23330051920060</v>
+        <v>23330051920067</v>
       </c>
       <c r="B19" t="s">
-        <v>141</v>
+        <v>65</v>
       </c>
       <c r="C19" t="s">
-        <v>23</v>
+        <v>156</v>
       </c>
       <c r="D19" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="E19" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F19">
         <v>-1</v>
@@ -8533,19 +8542,19 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20">
-        <v>23330051920061</v>
+        <v>23330051920068</v>
       </c>
       <c r="B20" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="C20" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="D20" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="E20" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F20">
         <v>-1</v>
@@ -8553,16 +8562,16 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21">
-        <v>23330051920061</v>
+        <v>23330051920069</v>
       </c>
       <c r="B21" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="C21" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="D21" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="E21" t="s">
         <v>36</v>
@@ -8573,16 +8582,16 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22">
-        <v>23330051920063</v>
+        <v>23330051920070</v>
       </c>
       <c r="B22" t="s">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="C22" t="s">
-        <v>11</v>
+        <v>159</v>
       </c>
       <c r="D22" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="E22" t="s">
         <v>36</v>
@@ -8593,19 +8602,19 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23">
-        <v>23330051920063</v>
+        <v>23330051920074</v>
       </c>
       <c r="B23" t="s">
-        <v>105</v>
+        <v>147</v>
       </c>
       <c r="C23" t="s">
-        <v>11</v>
+        <v>160</v>
       </c>
       <c r="D23" t="s">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="E23" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F23">
         <v>-1</v>
@@ -8613,19 +8622,19 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24">
-        <v>23330051920064</v>
+        <v>23330051920075</v>
       </c>
       <c r="B24" t="s">
-        <v>105</v>
+        <v>148</v>
       </c>
       <c r="C24" t="s">
-        <v>109</v>
+        <v>20</v>
       </c>
       <c r="D24" t="s">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="E24" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F24">
         <v>-1</v>
@@ -8633,16 +8642,16 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25">
-        <v>23330051920064</v>
+        <v>23330051920272</v>
       </c>
       <c r="B25" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="C25" t="s">
-        <v>109</v>
+        <v>69</v>
       </c>
       <c r="D25" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="E25" t="s">
         <v>36</v>
@@ -8653,361 +8662,21 @@
     </row>
     <row r="26" spans="1:6">
       <c r="A26">
-        <v>23330051920066</v>
+        <v>23330051920307</v>
       </c>
       <c r="B26" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="C26" t="s">
-        <v>111</v>
+        <v>161</v>
       </c>
       <c r="D26" t="s">
-        <v>172</v>
+        <v>133</v>
       </c>
       <c r="E26" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F26">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27">
-        <v>23330051920066</v>
-      </c>
-      <c r="B27" t="s">
-        <v>143</v>
-      </c>
-      <c r="C27" t="s">
-        <v>111</v>
-      </c>
-      <c r="D27" t="s">
-        <v>172</v>
-      </c>
-      <c r="E27" t="s">
-        <v>36</v>
-      </c>
-      <c r="F27">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28">
-        <v>23330051920067</v>
-      </c>
-      <c r="B28" t="s">
-        <v>65</v>
-      </c>
-      <c r="C28" t="s">
-        <v>154</v>
-      </c>
-      <c r="D28" t="s">
-        <v>173</v>
-      </c>
-      <c r="E28" t="s">
-        <v>36</v>
-      </c>
-      <c r="F28">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29">
-        <v>23330051920067</v>
-      </c>
-      <c r="B29" t="s">
-        <v>65</v>
-      </c>
-      <c r="C29" t="s">
-        <v>154</v>
-      </c>
-      <c r="D29" t="s">
-        <v>173</v>
-      </c>
-      <c r="E29" t="s">
-        <v>37</v>
-      </c>
-      <c r="F29">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30">
-        <v>23330051920068</v>
-      </c>
-      <c r="B30" t="s">
-        <v>144</v>
-      </c>
-      <c r="C30" t="s">
-        <v>155</v>
-      </c>
-      <c r="D30" t="s">
-        <v>174</v>
-      </c>
-      <c r="E30" t="s">
-        <v>36</v>
-      </c>
-      <c r="F30">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31">
-        <v>23330051920068</v>
-      </c>
-      <c r="B31" t="s">
-        <v>144</v>
-      </c>
-      <c r="C31" t="s">
-        <v>155</v>
-      </c>
-      <c r="D31" t="s">
-        <v>174</v>
-      </c>
-      <c r="E31" t="s">
-        <v>37</v>
-      </c>
-      <c r="F31">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32">
-        <v>23330051920069</v>
-      </c>
-      <c r="B32" t="s">
-        <v>145</v>
-      </c>
-      <c r="C32" t="s">
-        <v>156</v>
-      </c>
-      <c r="D32" t="s">
-        <v>175</v>
-      </c>
-      <c r="E32" t="s">
-        <v>37</v>
-      </c>
-      <c r="F32">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33">
-        <v>23330051920069</v>
-      </c>
-      <c r="B33" t="s">
-        <v>145</v>
-      </c>
-      <c r="C33" t="s">
-        <v>156</v>
-      </c>
-      <c r="D33" t="s">
-        <v>175</v>
-      </c>
-      <c r="E33" t="s">
-        <v>36</v>
-      </c>
-      <c r="F33">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34">
-        <v>23330051920070</v>
-      </c>
-      <c r="B34" t="s">
-        <v>116</v>
-      </c>
-      <c r="C34" t="s">
-        <v>157</v>
-      </c>
-      <c r="D34" t="s">
-        <v>176</v>
-      </c>
-      <c r="E34" t="s">
-        <v>36</v>
-      </c>
-      <c r="F34">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35">
-        <v>23330051920070</v>
-      </c>
-      <c r="B35" t="s">
-        <v>116</v>
-      </c>
-      <c r="C35" t="s">
-        <v>157</v>
-      </c>
-      <c r="D35" t="s">
-        <v>176</v>
-      </c>
-      <c r="E35" t="s">
-        <v>37</v>
-      </c>
-      <c r="F35">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36">
-        <v>23330051920074</v>
-      </c>
-      <c r="B36" t="s">
-        <v>146</v>
-      </c>
-      <c r="C36" t="s">
-        <v>158</v>
-      </c>
-      <c r="D36" t="s">
-        <v>177</v>
-      </c>
-      <c r="E36" t="s">
-        <v>37</v>
-      </c>
-      <c r="F36">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37">
-        <v>23330051920074</v>
-      </c>
-      <c r="B37" t="s">
-        <v>146</v>
-      </c>
-      <c r="C37" t="s">
-        <v>158</v>
-      </c>
-      <c r="D37" t="s">
-        <v>177</v>
-      </c>
-      <c r="E37" t="s">
-        <v>36</v>
-      </c>
-      <c r="F37">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38">
-        <v>23330051920075</v>
-      </c>
-      <c r="B38" t="s">
-        <v>147</v>
-      </c>
-      <c r="C38" t="s">
-        <v>20</v>
-      </c>
-      <c r="D38" t="s">
-        <v>178</v>
-      </c>
-      <c r="E38" t="s">
-        <v>36</v>
-      </c>
-      <c r="F38">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39">
-        <v>23330051920075</v>
-      </c>
-      <c r="B39" t="s">
-        <v>147</v>
-      </c>
-      <c r="C39" t="s">
-        <v>20</v>
-      </c>
-      <c r="D39" t="s">
-        <v>178</v>
-      </c>
-      <c r="E39" t="s">
-        <v>37</v>
-      </c>
-      <c r="F39">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="A40">
-        <v>23330051920272</v>
-      </c>
-      <c r="B40" t="s">
-        <v>109</v>
-      </c>
-      <c r="C40" t="s">
-        <v>69</v>
-      </c>
-      <c r="D40" t="s">
-        <v>179</v>
-      </c>
-      <c r="E40" t="s">
-        <v>37</v>
-      </c>
-      <c r="F40">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
-      <c r="A41">
-        <v>23330051920272</v>
-      </c>
-      <c r="B41" t="s">
-        <v>109</v>
-      </c>
-      <c r="C41" t="s">
-        <v>69</v>
-      </c>
-      <c r="D41" t="s">
-        <v>179</v>
-      </c>
-      <c r="E41" t="s">
-        <v>36</v>
-      </c>
-      <c r="F41">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
-      <c r="A42">
-        <v>23330051920307</v>
-      </c>
-      <c r="B42" t="s">
-        <v>148</v>
-      </c>
-      <c r="C42" t="s">
-        <v>159</v>
-      </c>
-      <c r="D42" t="s">
-        <v>133</v>
-      </c>
-      <c r="E42" t="s">
-        <v>36</v>
-      </c>
-      <c r="F42">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
-      <c r="A43">
-        <v>23330051920307</v>
-      </c>
-      <c r="B43" t="s">
-        <v>148</v>
-      </c>
-      <c r="C43" t="s">
-        <v>159</v>
-      </c>
-      <c r="D43" t="s">
-        <v>133</v>
-      </c>
-      <c r="E43" t="s">
-        <v>37</v>
-      </c>
-      <c r="F43">
         <v>-1</v>
       </c>
     </row>
@@ -9046,13 +8715,13 @@
         <v>22330051920007</v>
       </c>
       <c r="B2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C2" t="s">
         <v>17</v>
       </c>
       <c r="D2" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="E2" t="s">
         <v>95</v>
@@ -9066,13 +8735,13 @@
         <v>22330051920007</v>
       </c>
       <c r="B3" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C3" t="s">
         <v>17</v>
       </c>
       <c r="D3" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="E3" t="s">
         <v>36</v>
@@ -9086,13 +8755,13 @@
         <v>23330051920029</v>
       </c>
       <c r="B4" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C4" t="s">
         <v>17</v>
       </c>
       <c r="D4" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="E4" t="s">
         <v>36</v>
@@ -9106,13 +8775,13 @@
         <v>23330051920029</v>
       </c>
       <c r="B5" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C5" t="s">
         <v>17</v>
       </c>
       <c r="D5" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="E5" t="s">
         <v>95</v>
@@ -9126,19 +8795,19 @@
         <v>23330051920030</v>
       </c>
       <c r="B6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C6" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="D6" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="E6" t="s">
-        <v>36</v>
+        <v>95</v>
       </c>
       <c r="F6">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -9146,19 +8815,19 @@
         <v>23330051920030</v>
       </c>
       <c r="B7" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C7" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="D7" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="E7" t="s">
-        <v>95</v>
+        <v>36</v>
       </c>
       <c r="F7">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -9166,13 +8835,13 @@
         <v>23330051920031</v>
       </c>
       <c r="B8" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="C8" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="D8" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="E8" t="s">
         <v>36</v>
@@ -9186,13 +8855,13 @@
         <v>23330051920032</v>
       </c>
       <c r="B9" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="C9" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="D9" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="E9" t="s">
         <v>36</v>
@@ -9206,13 +8875,13 @@
         <v>23330051920032</v>
       </c>
       <c r="B10" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="C10" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="D10" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="E10" t="s">
         <v>95</v>
@@ -9226,13 +8895,13 @@
         <v>23330051920033</v>
       </c>
       <c r="B11" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="C11" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="D11" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="E11" t="s">
         <v>36</v>
@@ -9252,7 +8921,7 @@
         <v>11</v>
       </c>
       <c r="D12" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="E12" t="s">
         <v>36</v>
@@ -9269,10 +8938,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="s">
-        <v>193</v>
+        <v>143</v>
       </c>
       <c r="D13" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="E13" t="s">
         <v>36</v>
@@ -9289,10 +8958,10 @@
         <v>11</v>
       </c>
       <c r="C14" t="s">
-        <v>193</v>
+        <v>143</v>
       </c>
       <c r="D14" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="E14" t="s">
         <v>95</v>
@@ -9312,13 +8981,13 @@
         <v>24</v>
       </c>
       <c r="D15" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="E15" t="s">
-        <v>36</v>
+        <v>217</v>
       </c>
       <c r="F15">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -9332,13 +9001,13 @@
         <v>24</v>
       </c>
       <c r="D16" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="E16" t="s">
-        <v>214</v>
+        <v>36</v>
       </c>
       <c r="F16">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -9346,13 +9015,13 @@
         <v>23330051920040</v>
       </c>
       <c r="B17" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="C17" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="D17" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="E17" t="s">
         <v>36</v>
@@ -9369,7 +9038,7 @@
         <v>46</v>
       </c>
       <c r="C18" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="D18" t="s">
         <v>33</v>
@@ -9386,13 +9055,13 @@
         <v>23330051920042</v>
       </c>
       <c r="B19" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="C19" t="s">
         <v>42</v>
       </c>
       <c r="D19" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="E19" t="s">
         <v>36</v>
@@ -9409,10 +9078,10 @@
         <v>109</v>
       </c>
       <c r="C20" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="D20" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="E20" t="s">
         <v>36</v>
@@ -9426,13 +9095,13 @@
         <v>23330051920044</v>
       </c>
       <c r="B21" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="C21" t="s">
         <v>54</v>
       </c>
       <c r="D21" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="E21" t="s">
         <v>36</v>
@@ -9446,13 +9115,13 @@
         <v>23330051920046</v>
       </c>
       <c r="B22" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="C22" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="D22" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="E22" t="s">
         <v>36</v>
@@ -9466,13 +9135,13 @@
         <v>23330051920209</v>
       </c>
       <c r="B23" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="C23" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="D23" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="E23" t="s">
         <v>36</v>
@@ -9486,13 +9155,13 @@
         <v>23330051920232</v>
       </c>
       <c r="B24" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="C24" t="s">
         <v>42</v>
       </c>
       <c r="D24" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="E24" t="s">
         <v>36</v>
@@ -9533,36 +9202,36 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>23330051920117</v>
+        <v>22330061460232</v>
       </c>
       <c r="B2" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="C2" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="D2" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="E2" t="s">
-        <v>36</v>
+        <v>183</v>
       </c>
       <c r="F2">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>23330051920119</v>
+        <v>22330061460232</v>
       </c>
       <c r="B3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C3" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="D3" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="E3" t="s">
         <v>36</v>
@@ -9573,16 +9242,16 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>23330051920120</v>
+        <v>23330051920117</v>
       </c>
       <c r="B4" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C4" t="s">
-        <v>181</v>
+        <v>234</v>
       </c>
       <c r="D4" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="E4" t="s">
         <v>36</v>
@@ -9593,16 +9262,16 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>23330051920121</v>
+        <v>23330051920119</v>
       </c>
       <c r="B5" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C5" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="D5" t="s">
-        <v>161</v>
+        <v>252</v>
       </c>
       <c r="E5" t="s">
         <v>36</v>
@@ -9613,16 +9282,16 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>23330051920122</v>
+        <v>23330051920120</v>
       </c>
       <c r="B6" t="s">
-        <v>181</v>
+        <v>221</v>
       </c>
       <c r="C6" t="s">
-        <v>22</v>
+        <v>185</v>
       </c>
       <c r="D6" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="E6" t="s">
         <v>36</v>
@@ -9633,36 +9302,36 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>23330051920122</v>
+        <v>23330051920121</v>
       </c>
       <c r="B7" t="s">
-        <v>181</v>
+        <v>222</v>
       </c>
       <c r="C7" t="s">
-        <v>22</v>
+        <v>236</v>
       </c>
       <c r="D7" t="s">
-        <v>249</v>
+        <v>163</v>
       </c>
       <c r="E7" t="s">
-        <v>276</v>
+        <v>36</v>
       </c>
       <c r="F7">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>23330051920124</v>
+        <v>23330051920122</v>
       </c>
       <c r="B8" t="s">
-        <v>10</v>
+        <v>185</v>
       </c>
       <c r="C8" t="s">
-        <v>232</v>
+        <v>22</v>
       </c>
       <c r="D8" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="E8" t="s">
         <v>36</v>
@@ -9673,16 +9342,16 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>23330051920125</v>
+        <v>23330051920124</v>
       </c>
       <c r="B9" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C9" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="D9" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="E9" t="s">
         <v>36</v>
@@ -9693,16 +9362,16 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>23330051920126</v>
+        <v>23330051920125</v>
       </c>
       <c r="B10" t="s">
-        <v>219</v>
+        <v>17</v>
       </c>
       <c r="C10" t="s">
-        <v>14</v>
+        <v>155</v>
       </c>
       <c r="D10" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="E10" t="s">
         <v>36</v>
@@ -9713,16 +9382,16 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>23330051920127</v>
+        <v>23330051920126</v>
       </c>
       <c r="B11" t="s">
-        <v>11</v>
+        <v>223</v>
       </c>
       <c r="C11" t="s">
-        <v>234</v>
+        <v>14</v>
       </c>
       <c r="D11" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="E11" t="s">
         <v>36</v>
@@ -9733,16 +9402,16 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>23330051920128</v>
+        <v>23330051920127</v>
       </c>
       <c r="B12" t="s">
         <v>11</v>
       </c>
       <c r="C12" t="s">
-        <v>181</v>
+        <v>238</v>
       </c>
       <c r="D12" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="E12" t="s">
         <v>36</v>
@@ -9753,16 +9422,16 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>23330051920129</v>
+        <v>23330051920128</v>
       </c>
       <c r="B13" t="s">
         <v>11</v>
       </c>
       <c r="C13" t="s">
-        <v>45</v>
+        <v>185</v>
       </c>
       <c r="D13" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="E13" t="s">
         <v>36</v>
@@ -9773,16 +9442,16 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>23330051920130</v>
+        <v>23330051920129</v>
       </c>
       <c r="B14" t="s">
         <v>11</v>
       </c>
       <c r="C14" t="s">
-        <v>235</v>
+        <v>45</v>
       </c>
       <c r="D14" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="E14" t="s">
         <v>36</v>
@@ -9793,22 +9462,22 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>23330051920133</v>
+        <v>23330051920130</v>
       </c>
       <c r="B15" t="s">
-        <v>142</v>
+        <v>11</v>
       </c>
       <c r="C15" t="s">
-        <v>65</v>
+        <v>239</v>
       </c>
       <c r="D15" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="E15" t="s">
-        <v>277</v>
+        <v>36</v>
       </c>
       <c r="F15">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -9822,7 +9491,7 @@
         <v>65</v>
       </c>
       <c r="D16" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="E16" t="s">
         <v>36</v>
@@ -9833,36 +9502,36 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>23330051920134</v>
+        <v>23330051920133</v>
       </c>
       <c r="B17" t="s">
-        <v>23</v>
+        <v>142</v>
       </c>
       <c r="C17" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="D17" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="E17" t="s">
-        <v>36</v>
+        <v>183</v>
       </c>
       <c r="F17">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18">
-        <v>23330051920135</v>
+        <v>23330051920134</v>
       </c>
       <c r="B18" t="s">
         <v>23</v>
       </c>
       <c r="C18" t="s">
-        <v>236</v>
+        <v>11</v>
       </c>
       <c r="D18" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="E18" t="s">
         <v>36</v>
@@ -9873,16 +9542,16 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19">
-        <v>23330051920137</v>
+        <v>23330051920135</v>
       </c>
       <c r="B19" t="s">
-        <v>220</v>
+        <v>23</v>
       </c>
       <c r="C19" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="D19" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="E19" t="s">
         <v>36</v>
@@ -9893,16 +9562,16 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20">
-        <v>23330051920138</v>
+        <v>23330051920137</v>
       </c>
       <c r="B20" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="C20" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="D20" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="E20" t="s">
         <v>36</v>
@@ -9913,22 +9582,22 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21">
-        <v>23330051920139</v>
+        <v>23330051920138</v>
       </c>
       <c r="B21" t="s">
-        <v>105</v>
+        <v>225</v>
       </c>
       <c r="C21" t="s">
-        <v>101</v>
+        <v>242</v>
       </c>
       <c r="D21" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="E21" t="s">
-        <v>278</v>
+        <v>36</v>
       </c>
       <c r="F21">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -9942,7 +9611,7 @@
         <v>101</v>
       </c>
       <c r="D22" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="E22" t="s">
         <v>36</v>
@@ -9953,42 +9622,42 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23">
-        <v>23330051920140</v>
+        <v>23330051920139</v>
       </c>
       <c r="B23" t="s">
-        <v>222</v>
+        <v>105</v>
       </c>
       <c r="C23" t="s">
-        <v>233</v>
+        <v>101</v>
       </c>
       <c r="D23" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="E23" t="s">
-        <v>36</v>
+        <v>281</v>
       </c>
       <c r="F23">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24">
-        <v>23330051920141</v>
+        <v>23330051920140</v>
       </c>
       <c r="B24" t="s">
-        <v>19</v>
+        <v>226</v>
       </c>
       <c r="C24" t="s">
-        <v>239</v>
+        <v>155</v>
       </c>
       <c r="D24" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="E24" t="s">
-        <v>278</v>
+        <v>36</v>
       </c>
       <c r="F24">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -9999,10 +9668,10 @@
         <v>19</v>
       </c>
       <c r="C25" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="D25" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="E25" t="s">
         <v>36</v>
@@ -10013,36 +9682,36 @@
     </row>
     <row r="26" spans="1:6">
       <c r="A26">
-        <v>23330051920143</v>
+        <v>23330051920141</v>
       </c>
       <c r="B26" t="s">
-        <v>109</v>
+        <v>19</v>
       </c>
       <c r="C26" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="D26" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="E26" t="s">
-        <v>36</v>
+        <v>281</v>
       </c>
       <c r="F26">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27">
-        <v>23330051920144</v>
+        <v>23330051920143</v>
       </c>
       <c r="B27" t="s">
-        <v>223</v>
+        <v>109</v>
       </c>
       <c r="C27" t="s">
-        <v>223</v>
+        <v>244</v>
       </c>
       <c r="D27" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="E27" t="s">
         <v>36</v>
@@ -10053,22 +9722,22 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28">
-        <v>23330051920145</v>
+        <v>23330051920144</v>
       </c>
       <c r="B28" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="C28" t="s">
-        <v>14</v>
+        <v>227</v>
       </c>
       <c r="D28" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="E28" t="s">
-        <v>277</v>
+        <v>36</v>
       </c>
       <c r="F28">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="29" spans="1:6">
@@ -10076,33 +9745,33 @@
         <v>23330051920145</v>
       </c>
       <c r="B29" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="C29" t="s">
         <v>14</v>
       </c>
       <c r="D29" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="E29" t="s">
-        <v>36</v>
+        <v>183</v>
       </c>
       <c r="F29">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30">
-        <v>23330051920146</v>
+        <v>23330051920145</v>
       </c>
       <c r="B30" t="s">
+        <v>228</v>
+      </c>
+      <c r="C30" t="s">
         <v>14</v>
       </c>
-      <c r="C30" t="s">
-        <v>17</v>
-      </c>
       <c r="D30" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="E30" t="s">
         <v>36</v>
@@ -10113,16 +9782,16 @@
     </row>
     <row r="31" spans="1:6">
       <c r="A31">
-        <v>23330051920147</v>
+        <v>23330051920146</v>
       </c>
       <c r="B31" t="s">
-        <v>187</v>
+        <v>14</v>
       </c>
       <c r="C31" t="s">
-        <v>241</v>
+        <v>17</v>
       </c>
       <c r="D31" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="E31" t="s">
         <v>36</v>
@@ -10133,16 +9802,16 @@
     </row>
     <row r="32" spans="1:6">
       <c r="A32">
-        <v>23330051920149</v>
+        <v>23330051920147</v>
       </c>
       <c r="B32" t="s">
-        <v>225</v>
+        <v>191</v>
       </c>
       <c r="C32" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="D32" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="E32" t="s">
         <v>36</v>
@@ -10153,22 +9822,22 @@
     </row>
     <row r="33" spans="1:6">
       <c r="A33">
-        <v>23330051920150</v>
+        <v>23330051920149</v>
       </c>
       <c r="B33" t="s">
-        <v>16</v>
+        <v>229</v>
       </c>
       <c r="C33" t="s">
-        <v>48</v>
+        <v>246</v>
       </c>
       <c r="D33" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="E33" t="s">
-        <v>276</v>
+        <v>36</v>
       </c>
       <c r="F33">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="34" spans="1:6">
@@ -10182,7 +9851,7 @@
         <v>48</v>
       </c>
       <c r="D34" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="E34" t="s">
         <v>36</v>
@@ -10196,13 +9865,13 @@
         <v>23330051920255</v>
       </c>
       <c r="B35" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="C35" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="D35" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="E35" t="s">
         <v>36</v>
@@ -10219,10 +9888,10 @@
         <v>116</v>
       </c>
       <c r="C36" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="D36" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="E36" t="s">
         <v>36</v>
@@ -10236,13 +9905,13 @@
         <v>23330051920346</v>
       </c>
       <c r="B37" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="C37" t="s">
         <v>41</v>
       </c>
       <c r="D37" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="E37" t="s">
         <v>36</v>
@@ -10256,13 +9925,13 @@
         <v>23330061460223</v>
       </c>
       <c r="B38" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="C38" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="D38" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="E38" t="s">
         <v>36</v>
@@ -10306,16 +9975,16 @@
         <v>22330051920002</v>
       </c>
       <c r="B2" t="s">
-        <v>279</v>
+        <v>218</v>
       </c>
       <c r="C2" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="D2" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="E2" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -10332,10 +10001,10 @@
         <v>53</v>
       </c>
       <c r="D3" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="E3" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -10352,10 +10021,10 @@
         <v>53</v>
       </c>
       <c r="D4" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="E4" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -10369,13 +10038,13 @@
         <v>42</v>
       </c>
       <c r="C5" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="D5" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="E5" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -10389,13 +10058,13 @@
         <v>42</v>
       </c>
       <c r="C6" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="D6" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="E6" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -10406,16 +10075,16 @@
         <v>22330051920012</v>
       </c>
       <c r="B7" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C7" t="s">
         <v>14</v>
       </c>
       <c r="D7" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="E7" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -10429,13 +10098,13 @@
         <v>17</v>
       </c>
       <c r="C8" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="D8" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="E8" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -10449,13 +10118,13 @@
         <v>54</v>
       </c>
       <c r="C9" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="D9" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="E9" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -10469,13 +10138,13 @@
         <v>54</v>
       </c>
       <c r="C10" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="D10" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="E10" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -10489,13 +10158,13 @@
         <v>98</v>
       </c>
       <c r="C11" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="D11" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="E11" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -10506,16 +10175,16 @@
         <v>22330051920022</v>
       </c>
       <c r="B12" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="C12" t="s">
         <v>14</v>
       </c>
       <c r="D12" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="E12" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -10526,16 +10195,16 @@
         <v>22330051920173</v>
       </c>
       <c r="B13" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="C13" t="s">
         <v>62</v>
       </c>
       <c r="D13" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="E13" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -10546,16 +10215,16 @@
         <v>22330051920322</v>
       </c>
       <c r="B14" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="C14" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="D14" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="E14" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="F14">
         <v>5</v>
@@ -10599,13 +10268,13 @@
         <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="D2" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="E2" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -10616,16 +10285,16 @@
         <v>22330051920107</v>
       </c>
       <c r="B3" t="s">
+        <v>301</v>
+      </c>
+      <c r="C3" t="s">
+        <v>243</v>
+      </c>
+      <c r="D3" t="s">
+        <v>306</v>
+      </c>
+      <c r="E3" t="s">
         <v>299</v>
-      </c>
-      <c r="C3" t="s">
-        <v>239</v>
-      </c>
-      <c r="D3" t="s">
-        <v>304</v>
-      </c>
-      <c r="E3" t="s">
-        <v>297</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -10636,16 +10305,16 @@
         <v>22330051920116</v>
       </c>
       <c r="B4" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C4" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="D4" t="s">
         <v>138</v>
       </c>
       <c r="E4" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -10686,16 +10355,16 @@
         <v>21330051920112</v>
       </c>
       <c r="B2" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="C2" t="s">
         <v>116</v>
       </c>
       <c r="D2" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="E2" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -10706,16 +10375,16 @@
         <v>21330051920112</v>
       </c>
       <c r="B3" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="C3" t="s">
         <v>116</v>
       </c>
       <c r="D3" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="E3" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -10726,7 +10395,7 @@
         <v>22330051920153</v>
       </c>
       <c r="B4" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="C4" t="s">
         <v>13</v>
@@ -10735,7 +10404,7 @@
         <v>118</v>
       </c>
       <c r="E4" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -10746,7 +10415,7 @@
         <v>22330051920153</v>
       </c>
       <c r="B5" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="C5" t="s">
         <v>13</v>
@@ -10755,7 +10424,7 @@
         <v>118</v>
       </c>
       <c r="E5" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -10766,16 +10435,16 @@
         <v>22330051920162</v>
       </c>
       <c r="B6" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="C6" t="s">
         <v>109</v>
       </c>
       <c r="D6" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="E6" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -10786,16 +10455,16 @@
         <v>22330051920162</v>
       </c>
       <c r="B7" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="C7" t="s">
         <v>109</v>
       </c>
       <c r="D7" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="E7" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -10809,13 +10478,13 @@
         <v>62</v>
       </c>
       <c r="C8" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="D8" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="E8" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -10826,16 +10495,16 @@
         <v>22330051920282</v>
       </c>
       <c r="B9" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="C9" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="D9" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="E9" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -10846,16 +10515,16 @@
         <v>22330051920282</v>
       </c>
       <c r="B10" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="C10" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="D10" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="E10" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -10866,16 +10535,16 @@
         <v>22330051920367</v>
       </c>
       <c r="B11" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="C11" t="s">
         <v>42</v>
       </c>
       <c r="D11" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="E11" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -10886,16 +10555,16 @@
         <v>22330051920367</v>
       </c>
       <c r="B12" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="C12" t="s">
         <v>42</v>
       </c>
       <c r="D12" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="E12" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -10909,13 +10578,13 @@
         <v>116</v>
       </c>
       <c r="C13" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="D13" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="E13" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -10929,13 +10598,13 @@
         <v>116</v>
       </c>
       <c r="C14" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="D14" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="E14" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="F14">
         <v>5</v>

--- a/Rescatables20232.xlsx
+++ b/Rescatables20232.xlsx
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1042" uniqueCount="337">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1042" uniqueCount="340">
   <si>
     <t>Num_Cont</t>
   </si>
@@ -318,6 +318,9 @@
     <t>BASILIO</t>
   </si>
   <si>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
     <t>CORTES</t>
   </si>
   <si>
@@ -354,6 +357,9 @@
     <t>ESTEVEZ</t>
   </si>
   <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
     <t>DIAZ</t>
   </si>
   <si>
@@ -402,6 +408,9 @@
     <t>RICARDO</t>
   </si>
   <si>
+    <t>EDER</t>
+  </si>
+  <si>
     <t>LUIS FERNANDO</t>
   </si>
   <si>
@@ -474,450 +483,447 @@
     <t>ECOLOGÍA</t>
   </si>
   <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>LUGO</t>
+  </si>
+  <si>
+    <t>SOTO</t>
+  </si>
+  <si>
+    <t>ZAYRA</t>
+  </si>
+  <si>
+    <t>AHILY</t>
+  </si>
+  <si>
+    <t>ANDRES</t>
+  </si>
+  <si>
+    <t>INGLÉS IV</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>VICENTE</t>
+  </si>
+  <si>
+    <t>ALFONSO</t>
+  </si>
+  <si>
+    <t>LUNA</t>
+  </si>
+  <si>
+    <t>QUINTANA</t>
+  </si>
+  <si>
+    <t>DIEGO</t>
+  </si>
+  <si>
+    <t>JULIO</t>
+  </si>
+  <si>
+    <t>GUSTAVO</t>
+  </si>
+  <si>
+    <t>CRISTIAN</t>
+  </si>
+  <si>
+    <t>CÁLCULO DIFERENCIAL</t>
+  </si>
+  <si>
+    <t>CONSTRUYE PÁGINAS WEB</t>
+  </si>
+  <si>
+    <t>MENDOZA</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>ORTEGA</t>
+  </si>
+  <si>
+    <t>AYOHUA</t>
+  </si>
+  <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
+    <t>PALACIOS</t>
+  </si>
+  <si>
+    <t>GUTIERREZ</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>ESPARZA</t>
+  </si>
+  <si>
+    <t>COXCAHUA</t>
+  </si>
+  <si>
+    <t>EDUARDO</t>
+  </si>
+  <si>
+    <t>FATIMA</t>
+  </si>
+  <si>
+    <t>JOCELYN</t>
+  </si>
+  <si>
+    <t>DANA PAOLA</t>
+  </si>
+  <si>
+    <t>JOSE MIGUEL</t>
+  </si>
+  <si>
+    <t>CLAUDIA PAOLA</t>
+  </si>
+  <si>
+    <t>ANGELES VALERIA</t>
+  </si>
+  <si>
+    <t>JESUS ALEJANDRO</t>
+  </si>
+  <si>
+    <t>FRANCISCO JAVIER</t>
+  </si>
+  <si>
+    <t>KEVIN RAUL</t>
+  </si>
+  <si>
+    <t>GIL</t>
+  </si>
+  <si>
+    <t>PALOMINO</t>
+  </si>
+  <si>
+    <t>JENKINS</t>
+  </si>
+  <si>
+    <t>ACOSTA</t>
+  </si>
+  <si>
+    <t>CONTRERAS</t>
+  </si>
+  <si>
+    <t>JOSE RAUL</t>
+  </si>
+  <si>
+    <t>MIGUEL ANTONIO</t>
+  </si>
+  <si>
+    <t>AARON MIGUEL</t>
+  </si>
+  <si>
+    <t>ARTHUR RICHARD</t>
+  </si>
+  <si>
+    <t>JORGE IVAN</t>
+  </si>
+  <si>
+    <t>LOYO</t>
+  </si>
+  <si>
+    <t>ROSETE</t>
+  </si>
+  <si>
+    <t>MIXCOHUA</t>
+  </si>
+  <si>
+    <t>DIEGO ARMANDO</t>
+  </si>
+  <si>
+    <t>ROBERTO</t>
+  </si>
+  <si>
+    <t>YAHIR</t>
+  </si>
+  <si>
+    <t>TEMAS DE FÍSICA</t>
+  </si>
+  <si>
+    <t>TEMAS DE FILOSOFÍA</t>
+  </si>
+  <si>
+    <t>PROBABILIDAD Y ESTADÍSTICA</t>
+  </si>
+  <si>
+    <t>OFICIAL</t>
+  </si>
+  <si>
+    <t>PALOMARES</t>
+  </si>
+  <si>
+    <t>TZOPITL</t>
+  </si>
+  <si>
+    <t>TZOMPAXTLE</t>
+  </si>
+  <si>
+    <t>DE LOS SANTOS</t>
+  </si>
+  <si>
+    <t>ROSALES</t>
+  </si>
+  <si>
+    <t>JOSE MANUEL</t>
+  </si>
+  <si>
+    <t>CLEMENTE</t>
+  </si>
+  <si>
+    <t>JOSE ALEJANDRO</t>
+  </si>
+  <si>
+    <t>MORENO</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>NAHOMY</t>
+  </si>
+  <si>
+    <t>DIEGO EMILIO</t>
+  </si>
+  <si>
+    <t>SANTOS</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>CRISTOBAL</t>
+  </si>
+  <si>
+    <t>LAGUNA</t>
+  </si>
+  <si>
+    <t>GUEVARA</t>
+  </si>
+  <si>
+    <t>AUTRAN</t>
+  </si>
+  <si>
+    <t>CARRILLO</t>
+  </si>
+  <si>
+    <t>CIRUELO</t>
+  </si>
+  <si>
+    <t>SUAREZ</t>
+  </si>
+  <si>
+    <t>ANGEL CHARBEL</t>
+  </si>
+  <si>
+    <t>TRISTAN YABAL</t>
+  </si>
+  <si>
+    <t>JOSE ANTONIO</t>
+  </si>
+  <si>
+    <t>NATANAHEL</t>
+  </si>
+  <si>
+    <t>AXEL AARON</t>
+  </si>
+  <si>
+    <t>KEVYN DANIEL</t>
+  </si>
+  <si>
+    <t>LUIS FABIAN</t>
+  </si>
+  <si>
+    <t>SERGIO EDUARDO</t>
+  </si>
+  <si>
+    <t>SABDY</t>
+  </si>
+  <si>
+    <t>SERGIO JOSUE</t>
+  </si>
+  <si>
+    <t>Ingles II</t>
+  </si>
+  <si>
+    <t>MENDEZ</t>
+  </si>
+  <si>
+    <t>SAN JUAN</t>
+  </si>
+  <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>VEGA</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>FIGUEROA</t>
+  </si>
+  <si>
+    <t>TZITZIHUA</t>
+  </si>
+  <si>
+    <t>NATH</t>
+  </si>
+  <si>
+    <t>MONDRAGON</t>
+  </si>
+  <si>
+    <t>MARIANA</t>
+  </si>
+  <si>
+    <t>JAIRO</t>
+  </si>
+  <si>
+    <t>ALEXA YAMILET</t>
+  </si>
+  <si>
+    <t>MIRIAM</t>
+  </si>
+  <si>
+    <t>MARYSOL</t>
+  </si>
+  <si>
+    <t>AARON ZACHARY</t>
+  </si>
+  <si>
+    <t>DIANA LAURA</t>
+  </si>
+  <si>
+    <t>ANGEL ADRIAN</t>
+  </si>
+  <si>
+    <t>KARINA MONSERRATH</t>
+  </si>
+  <si>
+    <t>KARINA</t>
+  </si>
+  <si>
+    <t>FERNANDA YAMILET</t>
+  </si>
+  <si>
+    <t>MIREILLE</t>
+  </si>
+  <si>
+    <t>TOMA MUESTRAS BIOLÓGICAS</t>
+  </si>
+  <si>
+    <t>VALERIA</t>
+  </si>
+  <si>
+    <t>ABRAHAN</t>
+  </si>
+  <si>
+    <t>ZACARIAS</t>
+  </si>
+  <si>
+    <t>VALIENTE</t>
+  </si>
+  <si>
+    <t>DIEGO DE JESUS</t>
+  </si>
+  <si>
+    <t>ANGEL JESUS</t>
+  </si>
+  <si>
+    <t>ANGEL ABRAHAM</t>
+  </si>
+  <si>
+    <t>GISELA GUADALUPE</t>
+  </si>
+  <si>
+    <t>VANESSA</t>
+  </si>
+  <si>
+    <t>MARROQUIN</t>
+  </si>
+  <si>
+    <t>TINOCO</t>
+  </si>
+  <si>
+    <t>JULIO ALBERTO</t>
+  </si>
+  <si>
+    <t>NOHEMI ANGELICA</t>
+  </si>
+  <si>
+    <t>COBOS</t>
+  </si>
+  <si>
+    <t>MOLINA</t>
+  </si>
+  <si>
+    <t>NOLASCO</t>
+  </si>
+  <si>
+    <t>CABRERA</t>
+  </si>
+  <si>
+    <t>PLIEGO</t>
+  </si>
+  <si>
+    <t>YOLET</t>
+  </si>
+  <si>
+    <t>MARCO</t>
+  </si>
+  <si>
+    <t>DAVID</t>
+  </si>
+  <si>
+    <t>ARACELY</t>
+  </si>
+  <si>
+    <t>ERIK OMAR</t>
+  </si>
+  <si>
+    <t>VICTOR MANUEL</t>
+  </si>
+  <si>
+    <t>JOSUE GUSTAVO</t>
+  </si>
+  <si>
+    <t>ISRAEL</t>
+  </si>
+  <si>
+    <t>JAIRO YAIR</t>
+  </si>
+  <si>
+    <t>FABIAN ALEJANDRO</t>
+  </si>
+  <si>
     <t>PROGRAMA Y CONECTA CONTROLADORES LÓGICOS PROGRAMABLES (PLC´S)</t>
   </si>
   <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>LUGO</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>SOTO</t>
-  </si>
-  <si>
-    <t>ZAYRA</t>
-  </si>
-  <si>
-    <t>AHILY</t>
-  </si>
-  <si>
-    <t>ANDRES</t>
-  </si>
-  <si>
-    <t>INGLÉS IV</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>VICENTE</t>
-  </si>
-  <si>
-    <t>ALFONSO</t>
-  </si>
-  <si>
-    <t>LUNA</t>
-  </si>
-  <si>
-    <t>QUINTANA</t>
-  </si>
-  <si>
-    <t>DIEGO</t>
-  </si>
-  <si>
-    <t>JULIO</t>
-  </si>
-  <si>
-    <t>GUSTAVO</t>
-  </si>
-  <si>
-    <t>CRISTIAN</t>
-  </si>
-  <si>
-    <t>CÁLCULO DIFERENCIAL</t>
-  </si>
-  <si>
-    <t>CONSTRUYE PÁGINAS WEB</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>ORTEGA</t>
-  </si>
-  <si>
-    <t>AYOHUA</t>
-  </si>
-  <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>PALACIOS</t>
-  </si>
-  <si>
-    <t>GUTIERREZ</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>ESPARZA</t>
-  </si>
-  <si>
-    <t>COXCAHUA</t>
-  </si>
-  <si>
-    <t>EDUARDO</t>
-  </si>
-  <si>
-    <t>FATIMA</t>
-  </si>
-  <si>
-    <t>JOCELYN</t>
-  </si>
-  <si>
-    <t>DANA PAOLA</t>
-  </si>
-  <si>
-    <t>JOSE MIGUEL</t>
-  </si>
-  <si>
-    <t>CLAUDIA PAOLA</t>
-  </si>
-  <si>
-    <t>ANGELES VALERIA</t>
-  </si>
-  <si>
-    <t>JESUS ALEJANDRO</t>
-  </si>
-  <si>
-    <t>FRANCISCO JAVIER</t>
-  </si>
-  <si>
-    <t>KEVIN RAUL</t>
-  </si>
-  <si>
-    <t>GIL</t>
-  </si>
-  <si>
-    <t>PALOMINO</t>
-  </si>
-  <si>
-    <t>JENKINS</t>
-  </si>
-  <si>
-    <t>ACOSTA</t>
-  </si>
-  <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>JOSE RAUL</t>
-  </si>
-  <si>
-    <t>MIGUEL ANTONIO</t>
-  </si>
-  <si>
-    <t>AARON MIGUEL</t>
-  </si>
-  <si>
-    <t>ARTHUR RICHARD</t>
-  </si>
-  <si>
-    <t>JORGE IVAN</t>
-  </si>
-  <si>
-    <t>LOYO</t>
-  </si>
-  <si>
-    <t>ROSETE</t>
-  </si>
-  <si>
-    <t>MIXCOHUA</t>
-  </si>
-  <si>
-    <t>DIEGO ARMANDO</t>
-  </si>
-  <si>
-    <t>ROBERTO</t>
-  </si>
-  <si>
-    <t>YAHIR</t>
-  </si>
-  <si>
-    <t>TEMAS DE FÍSICA</t>
-  </si>
-  <si>
-    <t>TEMAS DE FILOSOFÍA</t>
-  </si>
-  <si>
-    <t>PROBABILIDAD Y ESTADÍSTICA</t>
-  </si>
-  <si>
-    <t>OFICIAL</t>
-  </si>
-  <si>
-    <t>PALOMARES</t>
-  </si>
-  <si>
-    <t>TZOPITL</t>
-  </si>
-  <si>
-    <t>TZOMPAXTLE</t>
-  </si>
-  <si>
-    <t>DE LOS SANTOS</t>
-  </si>
-  <si>
-    <t>ROSALES</t>
-  </si>
-  <si>
-    <t>JOSE MANUEL</t>
-  </si>
-  <si>
-    <t>CLEMENTE</t>
-  </si>
-  <si>
-    <t>JOSE ALEJANDRO</t>
-  </si>
-  <si>
-    <t>MORENO</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>NAHOMY</t>
-  </si>
-  <si>
-    <t>DIEGO EMILIO</t>
-  </si>
-  <si>
-    <t>SANTOS</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>CRISTOBAL</t>
-  </si>
-  <si>
-    <t>LAGUNA</t>
-  </si>
-  <si>
-    <t>GUEVARA</t>
-  </si>
-  <si>
-    <t>AUTRAN</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>CARRILLO</t>
-  </si>
-  <si>
-    <t>CIRUELO</t>
-  </si>
-  <si>
-    <t>SUAREZ</t>
-  </si>
-  <si>
-    <t>ANGEL CHARBEL</t>
-  </si>
-  <si>
-    <t>TRISTAN YABAL</t>
-  </si>
-  <si>
-    <t>JOSE ANTONIO</t>
-  </si>
-  <si>
-    <t>NATANAHEL</t>
-  </si>
-  <si>
-    <t>AXEL AARON</t>
-  </si>
-  <si>
-    <t>KEVYN DANIEL</t>
-  </si>
-  <si>
-    <t>LUIS FABIAN</t>
-  </si>
-  <si>
-    <t>SERGIO EDUARDO</t>
-  </si>
-  <si>
-    <t>SABDY</t>
-  </si>
-  <si>
-    <t>SERGIO JOSUE</t>
-  </si>
-  <si>
-    <t>Ingles II</t>
-  </si>
-  <si>
-    <t>CUAPIO</t>
-  </si>
-  <si>
-    <t>MENDEZ</t>
-  </si>
-  <si>
-    <t>SAN JUAN</t>
-  </si>
-  <si>
-    <t>VEGA</t>
+    <t>LLANOS</t>
+  </si>
+  <si>
+    <t>ANGELES</t>
+  </si>
+  <si>
+    <t>ARELLANO</t>
+  </si>
+  <si>
+    <t>BONILLA</t>
+  </si>
+  <si>
+    <t>DE ROMAN</t>
   </si>
   <si>
     <t>HUERTA</t>
   </si>
   <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>TZITZIHUA</t>
-  </si>
-  <si>
-    <t>NATH</t>
-  </si>
-  <si>
-    <t>MONDRAGON</t>
-  </si>
-  <si>
-    <t>JESSICA</t>
-  </si>
-  <si>
-    <t>REGINA DAYTRI</t>
-  </si>
-  <si>
-    <t>MARIANA</t>
-  </si>
-  <si>
-    <t>JAIRO</t>
-  </si>
-  <si>
-    <t>MIRIAM</t>
-  </si>
-  <si>
-    <t>MARYSOL</t>
-  </si>
-  <si>
-    <t>AARON ZACHARY</t>
-  </si>
-  <si>
-    <t>RAYMUNDO</t>
-  </si>
-  <si>
-    <t>DIANA LAURA</t>
-  </si>
-  <si>
-    <t>ANGEL ADRIAN</t>
-  </si>
-  <si>
-    <t>KARINA MONSERRATH</t>
-  </si>
-  <si>
-    <t>KARINA</t>
-  </si>
-  <si>
-    <t>MIREILLE</t>
-  </si>
-  <si>
-    <t>PREPARA SOLUCIONES PARA LAS OPERACIONES BÁSICAS DEL LABORATORIO</t>
-  </si>
-  <si>
-    <t>VALERIA</t>
-  </si>
-  <si>
-    <t>ABRAHAN</t>
-  </si>
-  <si>
-    <t>ZACARIAS</t>
-  </si>
-  <si>
-    <t>VALIENTE</t>
-  </si>
-  <si>
-    <t>DIEGO DE JESUS</t>
-  </si>
-  <si>
-    <t>ANGEL JESUS</t>
-  </si>
-  <si>
-    <t>ANGEL ABRAHAM</t>
-  </si>
-  <si>
-    <t>GISELA GUADALUPE</t>
-  </si>
-  <si>
-    <t>VANESSA</t>
-  </si>
-  <si>
-    <t>MARROQUIN</t>
-  </si>
-  <si>
-    <t>TINOCO</t>
-  </si>
-  <si>
-    <t>JULIO ALBERTO</t>
-  </si>
-  <si>
-    <t>NOHEMI ANGELICA</t>
-  </si>
-  <si>
-    <t>COBOS</t>
-  </si>
-  <si>
-    <t>MOLINA</t>
-  </si>
-  <si>
-    <t>NOLASCO</t>
-  </si>
-  <si>
-    <t>CABRERA</t>
-  </si>
-  <si>
-    <t>PLIEGO</t>
-  </si>
-  <si>
-    <t>YOLET</t>
-  </si>
-  <si>
-    <t>MARCO</t>
-  </si>
-  <si>
-    <t>DAVID</t>
-  </si>
-  <si>
-    <t>ARACELY</t>
-  </si>
-  <si>
-    <t>ERIK OMAR</t>
-  </si>
-  <si>
-    <t>VICTOR MANUEL</t>
-  </si>
-  <si>
-    <t>JOSUE GUSTAVO</t>
-  </si>
-  <si>
-    <t>ISRAEL</t>
-  </si>
-  <si>
-    <t>JAIRO YAIR</t>
-  </si>
-  <si>
-    <t>FABIAN ALEJANDRO</t>
-  </si>
-  <si>
-    <t>ANGELES</t>
-  </si>
-  <si>
-    <t>ARELLANO</t>
-  </si>
-  <si>
-    <t>BONILLA</t>
-  </si>
-  <si>
-    <t>DE ROMAN</t>
-  </si>
-  <si>
     <t>ROCHA</t>
   </si>
   <si>
@@ -927,6 +933,9 @@
     <t>IBAÑEZ</t>
   </si>
   <si>
+    <t>SERGIO</t>
+  </si>
+  <si>
     <t>AZURA</t>
   </si>
   <si>
@@ -942,10 +951,10 @@
     <t>BRENDA JANELY</t>
   </si>
   <si>
+    <t>NIDIA GABRIELA</t>
+  </si>
+  <si>
     <t>REALIZA ANÁLISIS CITOQUÍMICOS A LÍQUIDOS Y SECRECIONES CORPORALES</t>
-  </si>
-  <si>
-    <t>REALIZA ANÁLISIS HEMATOLÓGICOS DE SERIE ROJA</t>
   </si>
   <si>
     <t>FÍSICA I</t>
@@ -1652,16 +1661,16 @@
         <v>21330051920359</v>
       </c>
       <c r="B2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -1672,16 +1681,16 @@
         <v>22330051920054</v>
       </c>
       <c r="B3" t="s">
-        <v>145</v>
+        <v>90</v>
       </c>
       <c r="C3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E3" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -1692,16 +1701,16 @@
         <v>22330051920054</v>
       </c>
       <c r="B4" t="s">
-        <v>145</v>
+        <v>90</v>
       </c>
       <c r="C4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -1715,13 +1724,13 @@
         <v>63</v>
       </c>
       <c r="C5" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D5" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E5" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -1732,16 +1741,16 @@
         <v>22330051920071</v>
       </c>
       <c r="B6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -1752,16 +1761,16 @@
         <v>22330051920071</v>
       </c>
       <c r="B7" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C7" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D7" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E7" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -1772,16 +1781,16 @@
         <v>22330051920084</v>
       </c>
       <c r="B8" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C8" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D8" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E8" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -1792,16 +1801,16 @@
         <v>22330051920084</v>
       </c>
       <c r="B9" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D9" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E9" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -1812,16 +1821,16 @@
         <v>22330051920212</v>
       </c>
       <c r="B10" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C10" t="s">
         <v>32</v>
       </c>
       <c r="D10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -1832,16 +1841,16 @@
         <v>22330051920212</v>
       </c>
       <c r="B11" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C11" t="s">
         <v>32</v>
       </c>
       <c r="D11" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E11" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -1852,16 +1861,16 @@
         <v>22330051920218</v>
       </c>
       <c r="B12" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C12" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D12" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E12" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -1872,16 +1881,16 @@
         <v>22330051920317</v>
       </c>
       <c r="B13" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C13" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D13" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E13" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -1892,16 +1901,16 @@
         <v>22330051920317</v>
       </c>
       <c r="B14" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C14" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D14" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E14" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F14">
         <v>5</v>
@@ -1912,16 +1921,16 @@
         <v>22330051920333</v>
       </c>
       <c r="B15" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C15" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D15" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E15" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F15">
         <v>5</v>
@@ -1932,16 +1941,16 @@
         <v>22330051920333</v>
       </c>
       <c r="B16" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C16" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D16" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E16" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="F16">
         <v>5</v>
@@ -1958,10 +1967,10 @@
         <v>47</v>
       </c>
       <c r="D17" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E17" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F17">
         <v>5</v>
@@ -1974,7 +1983,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -2008,10 +2017,10 @@
         <v>30</v>
       </c>
       <c r="D2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E2" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -2022,16 +2031,16 @@
         <v>22330051920036</v>
       </c>
       <c r="B3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C3" t="s">
         <v>54</v>
       </c>
       <c r="D3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E3" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -2045,13 +2054,13 @@
         <v>44</v>
       </c>
       <c r="C4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D4" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E4" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -2065,13 +2074,13 @@
         <v>44</v>
       </c>
       <c r="C5" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D5" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E5" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -2082,16 +2091,16 @@
         <v>22330051920043</v>
       </c>
       <c r="B6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C6" t="s">
         <v>47</v>
       </c>
       <c r="D6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -2102,16 +2111,16 @@
         <v>22330051920189</v>
       </c>
       <c r="B7" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C7" t="s">
         <v>63</v>
       </c>
       <c r="D7" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E7" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -2119,41 +2128,21 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>22330051920189</v>
+        <v>22330051920327</v>
       </c>
       <c r="B8" t="s">
-        <v>184</v>
+        <v>55</v>
       </c>
       <c r="C8" t="s">
-        <v>63</v>
+        <v>187</v>
       </c>
       <c r="D8" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="E8" t="s">
-        <v>141</v>
+        <v>161</v>
       </c>
       <c r="F8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>22330051920327</v>
-      </c>
-      <c r="B9" t="s">
-        <v>55</v>
-      </c>
-      <c r="C9" t="s">
-        <v>186</v>
-      </c>
-      <c r="D9" t="s">
-        <v>191</v>
-      </c>
-      <c r="E9" t="s">
-        <v>160</v>
-      </c>
-      <c r="F9">
         <v>5</v>
       </c>
     </row>
@@ -2222,16 +2211,16 @@
         <v>21330051920164</v>
       </c>
       <c r="B2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C2" t="s">
         <v>12</v>
       </c>
       <c r="D2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -2242,16 +2231,16 @@
         <v>21330051920164</v>
       </c>
       <c r="B3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C3" t="s">
         <v>12</v>
       </c>
       <c r="D3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -2262,16 +2251,16 @@
         <v>21330051920165</v>
       </c>
       <c r="B4" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C4" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D4" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -2282,16 +2271,16 @@
         <v>21330051920165</v>
       </c>
       <c r="B5" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C5" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D5" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E5" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -2305,13 +2294,13 @@
         <v>8</v>
       </c>
       <c r="C6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -2445,13 +2434,13 @@
         <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -2465,13 +2454,13 @@
         <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D3" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -2482,16 +2471,16 @@
         <v>21330051920201</v>
       </c>
       <c r="B4" t="s">
+        <v>202</v>
+      </c>
+      <c r="C4" t="s">
+        <v>205</v>
+      </c>
+      <c r="D4" t="s">
+        <v>209</v>
+      </c>
+      <c r="E4" t="s">
         <v>201</v>
-      </c>
-      <c r="C4" t="s">
-        <v>204</v>
-      </c>
-      <c r="D4" t="s">
-        <v>208</v>
-      </c>
-      <c r="E4" t="s">
-        <v>200</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -2502,16 +2491,16 @@
         <v>21330051920202</v>
       </c>
       <c r="B5" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C5" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D5" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E5" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -2522,16 +2511,16 @@
         <v>21330051920202</v>
       </c>
       <c r="B6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -2545,13 +2534,13 @@
         <v>55</v>
       </c>
       <c r="C7" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D7" t="s">
         <v>83</v>
       </c>
       <c r="E7" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -2565,13 +2554,13 @@
         <v>55</v>
       </c>
       <c r="C8" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D8" t="s">
         <v>83</v>
       </c>
       <c r="E8" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -2585,13 +2574,13 @@
         <v>16</v>
       </c>
       <c r="C9" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D9" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E9" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -2605,13 +2594,13 @@
         <v>16</v>
       </c>
       <c r="C10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -2652,16 +2641,16 @@
         <v>19330051920208</v>
       </c>
       <c r="B2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -2678,10 +2667,10 @@
         <v>54</v>
       </c>
       <c r="D3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -2742,10 +2731,10 @@
         <v>22330051920196</v>
       </c>
       <c r="B3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C3" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D3" t="s">
         <v>225</v>
@@ -2762,10 +2751,10 @@
         <v>22330051920389</v>
       </c>
       <c r="B4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C4" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D4" t="s">
         <v>226</v>
@@ -2782,10 +2771,10 @@
         <v>23330051920189</v>
       </c>
       <c r="B5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C5" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D5" t="s">
         <v>227</v>
@@ -2802,10 +2791,10 @@
         <v>23330051920189</v>
       </c>
       <c r="B6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D6" t="s">
         <v>227</v>
@@ -2822,10 +2811,10 @@
         <v>23330051920190</v>
       </c>
       <c r="B7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C7" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D7" t="s">
         <v>228</v>
@@ -2842,10 +2831,10 @@
         <v>23330051920190</v>
       </c>
       <c r="B8" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C8" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D8" t="s">
         <v>228</v>
@@ -2885,7 +2874,7 @@
         <v>55</v>
       </c>
       <c r="C10" t="s">
-        <v>220</v>
+        <v>103</v>
       </c>
       <c r="D10" t="s">
         <v>230</v>
@@ -2902,7 +2891,7 @@
         <v>23330051920208</v>
       </c>
       <c r="B11" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C11" t="s">
         <v>46</v>
@@ -2922,7 +2911,7 @@
         <v>23330051920208</v>
       </c>
       <c r="B12" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C12" t="s">
         <v>46</v>
@@ -2942,13 +2931,13 @@
         <v>23330051920211</v>
       </c>
       <c r="B13" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C13" t="s">
         <v>221</v>
       </c>
       <c r="D13" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E13" t="s">
         <v>28</v>
@@ -3154,7 +3143,7 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -3179,10 +3168,10 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>23330051920222</v>
+        <v>23330051920229</v>
       </c>
       <c r="B2" t="s">
-        <v>235</v>
+        <v>63</v>
       </c>
       <c r="C2" t="s">
         <v>239</v>
@@ -3191,7 +3180,7 @@
         <v>244</v>
       </c>
       <c r="E2" t="s">
-        <v>257</v>
+        <v>28</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -3199,19 +3188,19 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>23330051920228</v>
+        <v>23330051920230</v>
       </c>
       <c r="B3" t="s">
         <v>63</v>
       </c>
       <c r="C3" t="s">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="D3" t="s">
         <v>245</v>
       </c>
       <c r="E3" t="s">
-        <v>72</v>
+        <v>28</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -3219,10 +3208,10 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>23330051920229</v>
+        <v>23330051920231</v>
       </c>
       <c r="B4" t="s">
-        <v>63</v>
+        <v>112</v>
       </c>
       <c r="C4" t="s">
         <v>240</v>
@@ -3231,7 +3220,7 @@
         <v>246</v>
       </c>
       <c r="E4" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -3239,19 +3228,19 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>23330051920230</v>
+        <v>23330051920231</v>
       </c>
       <c r="B5" t="s">
-        <v>63</v>
+        <v>112</v>
       </c>
       <c r="C5" t="s">
-        <v>214</v>
+        <v>240</v>
       </c>
       <c r="D5" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E5" t="s">
-        <v>28</v>
+        <v>256</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -3268,7 +3257,7 @@
         <v>241</v>
       </c>
       <c r="D6" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E6" t="s">
         <v>28</v>
@@ -3288,7 +3277,7 @@
         <v>241</v>
       </c>
       <c r="D7" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E7" t="s">
         <v>43</v>
@@ -3302,13 +3291,13 @@
         <v>23330051920241</v>
       </c>
       <c r="B8" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C8" t="s">
         <v>7</v>
       </c>
       <c r="D8" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E8" t="s">
         <v>43</v>
@@ -3322,16 +3311,16 @@
         <v>23330051920243</v>
       </c>
       <c r="B9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C9" t="s">
         <v>242</v>
       </c>
       <c r="D9" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E9" t="s">
-        <v>72</v>
+        <v>43</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -3339,13 +3328,13 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>23330051920243</v>
+        <v>23330051920249</v>
       </c>
       <c r="B10" t="s">
-        <v>217</v>
+        <v>127</v>
       </c>
       <c r="C10" t="s">
-        <v>242</v>
+        <v>62</v>
       </c>
       <c r="D10" t="s">
         <v>250</v>
@@ -3359,19 +3348,19 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>23330051920247</v>
+        <v>23330051920253</v>
       </c>
       <c r="B11" t="s">
-        <v>143</v>
+        <v>235</v>
       </c>
       <c r="C11" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="D11" t="s">
         <v>251</v>
       </c>
       <c r="E11" t="s">
-        <v>72</v>
+        <v>43</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -3379,13 +3368,13 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>23330051920249</v>
+        <v>23330051920264</v>
       </c>
       <c r="B12" t="s">
-        <v>124</v>
+        <v>236</v>
       </c>
       <c r="C12" t="s">
-        <v>62</v>
+        <v>212</v>
       </c>
       <c r="D12" t="s">
         <v>252</v>
@@ -3399,19 +3388,19 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>23330051920253</v>
+        <v>23330051920264</v>
       </c>
       <c r="B13" t="s">
         <v>236</v>
       </c>
       <c r="C13" t="s">
-        <v>243</v>
+        <v>212</v>
       </c>
       <c r="D13" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E13" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -3419,19 +3408,19 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>23330051920264</v>
+        <v>23330051920267</v>
       </c>
       <c r="B14" t="s">
-        <v>237</v>
+        <v>170</v>
       </c>
       <c r="C14" t="s">
-        <v>211</v>
+        <v>7</v>
       </c>
       <c r="D14" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="E14" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="F14">
         <v>5</v>
@@ -3439,19 +3428,19 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>23330051920264</v>
+        <v>23330051920267</v>
       </c>
       <c r="B15" t="s">
-        <v>237</v>
+        <v>170</v>
       </c>
       <c r="C15" t="s">
-        <v>211</v>
+        <v>7</v>
       </c>
       <c r="D15" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="E15" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="F15">
         <v>5</v>
@@ -3459,16 +3448,16 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>23330051920267</v>
+        <v>23330051920271</v>
       </c>
       <c r="B16" t="s">
-        <v>169</v>
+        <v>237</v>
       </c>
       <c r="C16" t="s">
-        <v>7</v>
+        <v>47</v>
       </c>
       <c r="D16" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E16" t="s">
         <v>43</v>
@@ -3479,19 +3468,19 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>23330051920267</v>
+        <v>23330051920271</v>
       </c>
       <c r="B17" t="s">
-        <v>169</v>
+        <v>237</v>
       </c>
       <c r="C17" t="s">
-        <v>7</v>
+        <v>47</v>
       </c>
       <c r="D17" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E17" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F17">
         <v>5</v>
@@ -3508,7 +3497,7 @@
         <v>30</v>
       </c>
       <c r="D18" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E18" t="s">
         <v>43</v>
@@ -3528,32 +3517,12 @@
         <v>34</v>
       </c>
       <c r="D19" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="E19" t="s">
         <v>43</v>
       </c>
       <c r="F19">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
-        <v>23330051920335</v>
-      </c>
-      <c r="B20" t="s">
-        <v>60</v>
-      </c>
-      <c r="C20" t="s">
-        <v>34</v>
-      </c>
-      <c r="D20" t="s">
-        <v>252</v>
-      </c>
-      <c r="E20" t="s">
-        <v>72</v>
-      </c>
-      <c r="F20">
         <v>5</v>
       </c>
     </row>
@@ -3598,7 +3567,7 @@
         <v>87</v>
       </c>
       <c r="D2" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E2" t="s">
         <v>43</v>
@@ -3612,13 +3581,13 @@
         <v>23330051920365</v>
       </c>
       <c r="B3" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D3" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E3" t="s">
         <v>43</v>
@@ -3632,13 +3601,13 @@
         <v>23330051920365</v>
       </c>
       <c r="B4" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D4" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E4" t="s">
         <v>234</v>
@@ -3685,10 +3654,10 @@
         <v>63</v>
       </c>
       <c r="C2" t="s">
+        <v>260</v>
+      </c>
+      <c r="D2" t="s">
         <v>261</v>
-      </c>
-      <c r="D2" t="s">
-        <v>262</v>
       </c>
       <c r="E2" t="s">
         <v>28</v>
@@ -3708,7 +3677,7 @@
         <v>58</v>
       </c>
       <c r="D3" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E3" t="s">
         <v>27</v>
@@ -3728,7 +3697,7 @@
         <v>58</v>
       </c>
       <c r="D4" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E4" t="s">
         <v>28</v>
@@ -3742,13 +3711,13 @@
         <v>23330051920280</v>
       </c>
       <c r="B5" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C5" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="D5" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E5" t="s">
         <v>28</v>
@@ -3762,13 +3731,13 @@
         <v>23330051920328</v>
       </c>
       <c r="B6" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C6" t="s">
         <v>222</v>
       </c>
       <c r="D6" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E6" t="s">
         <v>27</v>
@@ -3782,13 +3751,13 @@
         <v>23330051920357</v>
       </c>
       <c r="B7" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C7" t="s">
         <v>30</v>
       </c>
       <c r="D7" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E7" t="s">
         <v>28</v>
@@ -3804,7 +3773,7 @@
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -3832,13 +3801,13 @@
         <v>23330051920289</v>
       </c>
       <c r="B2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E2" t="s">
         <v>72</v>
@@ -3852,13 +3821,13 @@
         <v>23330051920290</v>
       </c>
       <c r="B3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C3" t="s">
+        <v>267</v>
+      </c>
+      <c r="D3" t="s">
         <v>268</v>
-      </c>
-      <c r="D3" t="s">
-        <v>269</v>
       </c>
       <c r="E3" t="s">
         <v>72</v>
@@ -3875,35 +3844,15 @@
         <v>55</v>
       </c>
       <c r="C4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D4" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="E4" t="s">
         <v>28</v>
       </c>
       <c r="F4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>23330051920303</v>
-      </c>
-      <c r="B5" t="s">
-        <v>55</v>
-      </c>
-      <c r="C5" t="s">
-        <v>96</v>
-      </c>
-      <c r="D5" t="s">
-        <v>270</v>
-      </c>
-      <c r="E5" t="s">
-        <v>72</v>
-      </c>
-      <c r="F5">
         <v>5</v>
       </c>
     </row>
@@ -3942,16 +3891,16 @@
         <v>21330051920007</v>
       </c>
       <c r="B2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E2" t="s">
-        <v>142</v>
+        <v>285</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -3962,16 +3911,16 @@
         <v>21330051920007</v>
       </c>
       <c r="B3" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C3" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D3" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -3985,13 +3934,13 @@
         <v>59</v>
       </c>
       <c r="C4" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D4" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E4" t="s">
-        <v>142</v>
+        <v>285</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -4008,10 +3957,10 @@
         <v>53</v>
       </c>
       <c r="D5" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E5" t="s">
-        <v>142</v>
+        <v>285</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -4028,10 +3977,10 @@
         <v>222</v>
       </c>
       <c r="D6" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -4048,10 +3997,10 @@
         <v>222</v>
       </c>
       <c r="D7" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E7" t="s">
-        <v>142</v>
+        <v>285</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -4062,16 +4011,16 @@
         <v>22330051920192</v>
       </c>
       <c r="B8" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C8" t="s">
         <v>47</v>
       </c>
       <c r="D8" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E8" t="s">
-        <v>142</v>
+        <v>285</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -4082,16 +4031,16 @@
         <v>22330051920193</v>
       </c>
       <c r="B9" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C9" t="s">
-        <v>220</v>
+        <v>103</v>
       </c>
       <c r="D9" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E9" t="s">
-        <v>142</v>
+        <v>285</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -4102,16 +4051,16 @@
         <v>22330051920356</v>
       </c>
       <c r="B10" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C10" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D10" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E10" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -4128,10 +4077,10 @@
         <v>30</v>
       </c>
       <c r="D11" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="E11" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -4142,16 +4091,16 @@
         <v>22330051920378</v>
       </c>
       <c r="B12" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C12" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D12" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E12" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -4168,10 +4117,10 @@
         <v>34</v>
       </c>
       <c r="D13" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -4184,7 +4133,7 @@
 
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -4209,19 +4158,19 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>22330051920230</v>
+        <v>21330051420317</v>
       </c>
       <c r="B2" t="s">
         <v>286</v>
       </c>
       <c r="C2" t="s">
-        <v>290</v>
+        <v>239</v>
       </c>
       <c r="D2" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="E2" t="s">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -4229,19 +4178,19 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>22330051920231</v>
+        <v>21330051420317</v>
       </c>
       <c r="B3" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C3" t="s">
-        <v>291</v>
+        <v>239</v>
       </c>
       <c r="D3" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="E3" t="s">
-        <v>298</v>
+        <v>151</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -4249,19 +4198,19 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>22330051920231</v>
+        <v>22330051920230</v>
       </c>
       <c r="B4" t="s">
         <v>287</v>
       </c>
       <c r="C4" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D4" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="E4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -4269,19 +4218,19 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>22330051920233</v>
+        <v>22330051920231</v>
       </c>
       <c r="B5" t="s">
         <v>288</v>
       </c>
       <c r="C5" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D5" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="E5" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -4292,16 +4241,16 @@
         <v>22330051920233</v>
       </c>
       <c r="B6" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C6" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="D6" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="E6" t="s">
-        <v>299</v>
+        <v>151</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -4312,16 +4261,16 @@
         <v>22330051920235</v>
       </c>
       <c r="B7" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D7" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="E7" t="s">
-        <v>150</v>
+        <v>302</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -4332,16 +4281,16 @@
         <v>22330051920235</v>
       </c>
       <c r="B8" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C8" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D8" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="E8" t="s">
-        <v>298</v>
+        <v>151</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -4355,15 +4304,55 @@
         <v>11</v>
       </c>
       <c r="C9" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D9" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="E9" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="F9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10">
+        <v>22330051920369</v>
+      </c>
+      <c r="B10" t="s">
+        <v>291</v>
+      </c>
+      <c r="C10" t="s">
+        <v>16</v>
+      </c>
+      <c r="D10" t="s">
+        <v>301</v>
+      </c>
+      <c r="E10" t="s">
+        <v>151</v>
+      </c>
+      <c r="F10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11">
+        <v>22330051920369</v>
+      </c>
+      <c r="B11" t="s">
+        <v>291</v>
+      </c>
+      <c r="C11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D11" t="s">
+        <v>301</v>
+      </c>
+      <c r="E11" t="s">
+        <v>303</v>
+      </c>
+      <c r="F11">
         <v>5</v>
       </c>
     </row>
@@ -4405,13 +4394,13 @@
         <v>79</v>
       </c>
       <c r="C2" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="D2" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="E2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -4425,13 +4414,13 @@
         <v>79</v>
       </c>
       <c r="C3" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="D3" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="E3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -4448,10 +4437,10 @@
         <v>47</v>
       </c>
       <c r="D4" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="E4" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -4468,10 +4457,10 @@
         <v>47</v>
       </c>
       <c r="D5" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="E5" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -4488,10 +4477,10 @@
         <v>47</v>
       </c>
       <c r="D6" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="E6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -4562,16 +4551,16 @@
         <v>22330051920312</v>
       </c>
       <c r="B2" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="C2" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="D2" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="E2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -4582,16 +4571,16 @@
         <v>22330051920314</v>
       </c>
       <c r="B3" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C3" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="D3" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="E3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -4608,10 +4597,10 @@
         <v>47</v>
       </c>
       <c r="D4" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="E4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -4622,16 +4611,16 @@
         <v>22330051920397</v>
       </c>
       <c r="B5" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C5" t="s">
         <v>79</v>
       </c>
       <c r="D5" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="E5" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -4675,13 +4664,13 @@
         <v>30</v>
       </c>
       <c r="C2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D2" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="E2" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -4692,16 +4681,16 @@
         <v>20330051920366</v>
       </c>
       <c r="B3" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="C3" t="s">
         <v>30</v>
       </c>
       <c r="D3" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="E3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -4712,7 +4701,7 @@
         <v>20330051920367</v>
       </c>
       <c r="B4" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="C4" t="s">
         <v>30</v>
@@ -4721,7 +4710,7 @@
         <v>82</v>
       </c>
       <c r="E4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -4732,16 +4721,16 @@
         <v>21330051920021</v>
       </c>
       <c r="B5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C5" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="D5" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E5" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -4915,13 +4904,13 @@
         <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="D2" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="E2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -4935,13 +4924,13 @@
         <v>34</v>
       </c>
       <c r="C3" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="D3" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="E3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -4952,16 +4941,16 @@
         <v>21330051920075</v>
       </c>
       <c r="B4" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="C4" t="s">
         <v>13</v>
       </c>
       <c r="D4" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="E4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -4978,10 +4967,10 @@
         <v>30</v>
       </c>
       <c r="D5" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="E5" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -4998,10 +4987,10 @@
         <v>15</v>
       </c>
       <c r="D6" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="E6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -5012,16 +5001,16 @@
         <v>21330051920109</v>
       </c>
       <c r="B7" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C7" t="s">
         <v>62</v>
       </c>
       <c r="D7" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="E7" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -5032,16 +5021,16 @@
         <v>21330051920109</v>
       </c>
       <c r="B8" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C8" t="s">
         <v>62</v>
       </c>
       <c r="D8" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="E8" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -5058,10 +5047,10 @@
         <v>59</v>
       </c>
       <c r="D9" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="E9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -5105,13 +5094,13 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D2" t="s">
         <v>226</v>
       </c>
       <c r="E2" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -5152,16 +5141,16 @@
         <v>20330051920132</v>
       </c>
       <c r="B2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C2" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="D2" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="E2" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -5172,16 +5161,16 @@
         <v>20330051920132</v>
       </c>
       <c r="B3" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C3" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="D3" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="E3" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -5198,10 +5187,10 @@
         <v>53</v>
       </c>
       <c r="D4" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="E4" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -5212,16 +5201,16 @@
         <v>21330051920390</v>
       </c>
       <c r="B5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C5" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="D5" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="E5" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -5268,10 +5257,10 @@
         <v>32</v>
       </c>
       <c r="D2" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="E2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -5288,10 +5277,10 @@
         <v>32</v>
       </c>
       <c r="D3" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="E3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -5302,16 +5291,16 @@
         <v>21330051920382</v>
       </c>
       <c r="B4" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="C4" t="s">
         <v>47</v>
       </c>
       <c r="D4" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="E4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -5322,16 +5311,16 @@
         <v>21330051920382</v>
       </c>
       <c r="B5" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="C5" t="s">
         <v>47</v>
       </c>
       <c r="D5" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="E5" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -5721,7 +5710,7 @@
         <v>84</v>
       </c>
       <c r="E6" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -5741,7 +5730,7 @@
         <v>84</v>
       </c>
       <c r="E7" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -5794,7 +5783,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -5825,13 +5814,13 @@
         <v>73</v>
       </c>
       <c r="C2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E2" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -5848,10 +5837,10 @@
         <v>33</v>
       </c>
       <c r="D3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E3" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -5868,10 +5857,10 @@
         <v>33</v>
       </c>
       <c r="D4" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E4" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -5885,13 +5874,13 @@
         <v>88</v>
       </c>
       <c r="C5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D5" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E5" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -5905,13 +5894,13 @@
         <v>89</v>
       </c>
       <c r="C6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D6" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E6" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -5919,19 +5908,19 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>22330051920009</v>
+        <v>22330051920006</v>
       </c>
       <c r="B7" t="s">
         <v>90</v>
       </c>
       <c r="C7" t="s">
-        <v>53</v>
+        <v>103</v>
       </c>
       <c r="D7" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E7" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -5939,19 +5928,19 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>22330051920012</v>
+        <v>22330051920006</v>
       </c>
       <c r="B8" t="s">
-        <v>17</v>
+        <v>90</v>
       </c>
       <c r="C8" t="s">
-        <v>54</v>
+        <v>103</v>
       </c>
       <c r="D8" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E8" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -5959,19 +5948,19 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>22330051920013</v>
+        <v>22330051920009</v>
       </c>
       <c r="B9" t="s">
         <v>91</v>
       </c>
       <c r="C9" t="s">
-        <v>102</v>
+        <v>53</v>
       </c>
       <c r="D9" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E9" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -5979,19 +5968,19 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>22330051920014</v>
+        <v>22330051920012</v>
       </c>
       <c r="B10" t="s">
-        <v>63</v>
+        <v>17</v>
       </c>
       <c r="C10" t="s">
-        <v>103</v>
+        <v>54</v>
       </c>
       <c r="D10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E10" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -5999,19 +5988,19 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>22330051920015</v>
+        <v>22330051920013</v>
       </c>
       <c r="B11" t="s">
-        <v>63</v>
+        <v>92</v>
       </c>
       <c r="C11" t="s">
         <v>104</v>
       </c>
       <c r="D11" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E11" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -6019,19 +6008,19 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>22330051920015</v>
+        <v>22330051920014</v>
       </c>
       <c r="B12" t="s">
         <v>63</v>
       </c>
       <c r="C12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D12" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E12" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -6039,19 +6028,19 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>22330051920016</v>
+        <v>22330051920015</v>
       </c>
       <c r="B13" t="s">
-        <v>30</v>
+        <v>63</v>
       </c>
       <c r="C13" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D13" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E13" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -6059,19 +6048,19 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>22330051920017</v>
+        <v>22330051920015</v>
       </c>
       <c r="B14" t="s">
-        <v>92</v>
+        <v>63</v>
       </c>
       <c r="C14" t="s">
         <v>106</v>
       </c>
       <c r="D14" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E14" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F14">
         <v>5</v>
@@ -6079,19 +6068,19 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>22330051920017</v>
+        <v>22330051920016</v>
       </c>
       <c r="B15" t="s">
-        <v>92</v>
+        <v>30</v>
       </c>
       <c r="C15" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D15" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E15" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="F15">
         <v>5</v>
@@ -6099,19 +6088,19 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>22330051920018</v>
+        <v>22330051920017</v>
       </c>
       <c r="B16" t="s">
-        <v>44</v>
+        <v>93</v>
       </c>
       <c r="C16" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D16" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E16" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="F16">
         <v>5</v>
@@ -6119,19 +6108,19 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>22330051920020</v>
+        <v>22330051920017</v>
       </c>
       <c r="B17" t="s">
         <v>93</v>
       </c>
       <c r="C17" t="s">
-        <v>79</v>
+        <v>108</v>
       </c>
       <c r="D17" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E17" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="F17">
         <v>5</v>
@@ -6139,19 +6128,19 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18">
-        <v>22330051920022</v>
+        <v>22330051920018</v>
       </c>
       <c r="B18" t="s">
-        <v>94</v>
+        <v>44</v>
       </c>
       <c r="C18" t="s">
-        <v>54</v>
+        <v>109</v>
       </c>
       <c r="D18" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E18" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="F18">
         <v>5</v>
@@ -6159,19 +6148,19 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19">
-        <v>22330051920023</v>
+        <v>22330051920020</v>
       </c>
       <c r="B19" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C19" t="s">
-        <v>108</v>
+        <v>79</v>
       </c>
       <c r="D19" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E19" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="F19">
         <v>5</v>
@@ -6179,19 +6168,19 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20">
-        <v>22330051920024</v>
+        <v>22330051920022</v>
       </c>
       <c r="B20" t="s">
-        <v>19</v>
+        <v>95</v>
       </c>
       <c r="C20" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D20" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E20" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="F20">
         <v>5</v>
@@ -6199,19 +6188,19 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21">
-        <v>22330051920025</v>
+        <v>22330051920023</v>
       </c>
       <c r="B21" t="s">
         <v>96</v>
       </c>
       <c r="C21" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D21" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E21" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="F21">
         <v>5</v>
@@ -6219,19 +6208,19 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22">
-        <v>22330051920026</v>
+        <v>22330051920024</v>
       </c>
       <c r="B22" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C22" t="s">
-        <v>110</v>
+        <v>53</v>
       </c>
       <c r="D22" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E22" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="F22">
         <v>5</v>
@@ -6239,19 +6228,19 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23">
-        <v>22330051920027</v>
+        <v>22330051920025</v>
       </c>
       <c r="B23" t="s">
-        <v>54</v>
+        <v>97</v>
       </c>
       <c r="C23" t="s">
         <v>111</v>
       </c>
       <c r="D23" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E23" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="F23">
         <v>5</v>
@@ -6259,19 +6248,19 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24">
-        <v>22330051920173</v>
+        <v>22330051920026</v>
       </c>
       <c r="B24" t="s">
         <v>12</v>
       </c>
       <c r="C24" t="s">
-        <v>19</v>
+        <v>112</v>
       </c>
       <c r="D24" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E24" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="F24">
         <v>5</v>
@@ -6279,19 +6268,19 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25">
-        <v>22330051920320</v>
+        <v>22330051920027</v>
       </c>
       <c r="B25" t="s">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="C25" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D25" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E25" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="F25">
         <v>5</v>
@@ -6299,19 +6288,19 @@
     </row>
     <row r="26" spans="1:6">
       <c r="A26">
-        <v>22330051920322</v>
+        <v>22330051920173</v>
       </c>
       <c r="B26" t="s">
-        <v>97</v>
+        <v>12</v>
       </c>
       <c r="C26" t="s">
-        <v>113</v>
+        <v>19</v>
       </c>
       <c r="D26" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E26" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="F26">
         <v>5</v>
@@ -6319,19 +6308,19 @@
     </row>
     <row r="27" spans="1:6">
       <c r="A27">
-        <v>22330051920326</v>
+        <v>22330051920320</v>
       </c>
       <c r="B27" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="C27" t="s">
-        <v>59</v>
+        <v>114</v>
       </c>
       <c r="D27" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E27" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="F27">
         <v>5</v>
@@ -6339,19 +6328,19 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28">
-        <v>22330051920330</v>
+        <v>22330051920322</v>
       </c>
       <c r="B28" t="s">
-        <v>12</v>
+        <v>98</v>
       </c>
       <c r="C28" t="s">
-        <v>54</v>
+        <v>115</v>
       </c>
       <c r="D28" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E28" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="F28">
         <v>5</v>
@@ -6359,19 +6348,19 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29">
-        <v>22330051920332</v>
+        <v>22330051920326</v>
       </c>
       <c r="B29" t="s">
-        <v>98</v>
+        <v>12</v>
       </c>
       <c r="C29" t="s">
-        <v>93</v>
+        <v>59</v>
       </c>
       <c r="D29" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E29" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="F29">
         <v>5</v>
@@ -6379,19 +6368,19 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30">
-        <v>22330051920382</v>
+        <v>22330051920330</v>
       </c>
       <c r="B30" t="s">
-        <v>93</v>
+        <v>12</v>
       </c>
       <c r="C30" t="s">
-        <v>114</v>
+        <v>54</v>
       </c>
       <c r="D30" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E30" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F30">
         <v>5</v>
@@ -6399,21 +6388,41 @@
     </row>
     <row r="31" spans="1:6">
       <c r="A31">
+        <v>22330051920332</v>
+      </c>
+      <c r="B31" t="s">
+        <v>99</v>
+      </c>
+      <c r="C31" t="s">
+        <v>94</v>
+      </c>
+      <c r="D31" t="s">
+        <v>141</v>
+      </c>
+      <c r="E31" t="s">
+        <v>143</v>
+      </c>
+      <c r="F31">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6">
+      <c r="A32">
         <v>22330051920382</v>
       </c>
-      <c r="B31" t="s">
-        <v>93</v>
-      </c>
-      <c r="C31" t="s">
-        <v>114</v>
-      </c>
-      <c r="D31" t="s">
-        <v>139</v>
-      </c>
-      <c r="E31" t="s">
-        <v>140</v>
-      </c>
-      <c r="F31">
+      <c r="B32" t="s">
+        <v>94</v>
+      </c>
+      <c r="C32" t="s">
+        <v>116</v>
+      </c>
+      <c r="D32" t="s">
+        <v>142</v>
+      </c>
+      <c r="E32" t="s">
+        <v>143</v>
+      </c>
+      <c r="F32">
         <v>5</v>
       </c>
     </row>
@@ -6452,16 +6461,16 @@
         <v>22330051920100</v>
       </c>
       <c r="B2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="D2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -6475,13 +6484,13 @@
         <v>36</v>
       </c>
       <c r="C3" t="s">
-        <v>145</v>
+        <v>90</v>
       </c>
       <c r="D3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -6495,13 +6504,13 @@
         <v>53</v>
       </c>
       <c r="C4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E4" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -6545,13 +6554,13 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -6565,13 +6574,13 @@
         <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -6582,16 +6591,16 @@
         <v>22330051920386</v>
       </c>
       <c r="B4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -6602,16 +6611,16 @@
         <v>22330051920426</v>
       </c>
       <c r="B5" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C5" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D5" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E5" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F5">
         <v>5</v>
